--- a/financial_models/opportunities/1929.HK_Valuation.xlsx
+++ b/financial_models/opportunities/1929.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F82BF80-29BD-4653-B925-A0120DDE43E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EFBD2D1-7A73-4A74-876E-65D652A05F79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33720" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="33720" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="516" uniqueCount="349">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="520" uniqueCount="350">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -218,10 +218,6 @@
   </si>
   <si>
     <t>ROE</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>EBIT ROE</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -658,10 +654,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>EBIT/Sales</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Total Assets/Equity</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -683,10 +675,6 @@
   </si>
   <si>
     <t>Balance Sheet Analysis</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>FCFE/Market Price</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -871,10 +859,6 @@
   </si>
   <si>
     <t>/Equity Cost of Capital</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>- Interest Bearing Debt</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1429,6 +1413,26 @@
   </si>
   <si>
     <t>Operating Asset % of Sales</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>After-tax Profit/Market Price</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pre-tax Profit/Sales</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pre-tax Profit ROE</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Market Price Attractiveness</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>- Net Debt</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1938,7 +1942,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="268">
+  <cellXfs count="267">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -2505,17 +2509,14 @@
     </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="8" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="8" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="190" fontId="8" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2814,30 +2815,30 @@
   <sheetData>
     <row r="1" spans="1:9" ht="12.4" x14ac:dyDescent="0.4">
       <c r="B1" s="50" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C1" s="204" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="D1" s="54" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B2" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C2" s="46">
         <v>45643</v>
       </c>
       <c r="D2" s="57"/>
       <c r="E2" s="106" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A3" s="37" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B3" s="37"/>
       <c r="C3" s="37"/>
@@ -2850,22 +2851,22 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B4" s="48" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C4" s="49"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B5" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C5" s="26" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="D5" s="2"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B6" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C6" s="47">
         <v>8</v>
@@ -2874,7 +2875,7 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B7" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C7" s="34">
         <f>EOMONTH(EDATE(BS!C1,Thesis!C6),0)</f>
@@ -2891,13 +2892,13 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B10" s="4" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C10" s="55">
         <v>9.06</v>
       </c>
       <c r="D10" s="53" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.35">
@@ -2914,7 +2915,7 @@
         <v>1</v>
       </c>
       <c r="C12" s="53" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="D12" s="33"/>
     </row>
@@ -2945,7 +2946,7 @@
     </row>
     <row r="16" spans="1:9" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A16" s="37" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B16" s="37"/>
       <c r="C16" s="37"/>
@@ -2958,22 +2959,22 @@
         <v>1.</v>
       </c>
       <c r="B18" s="50" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B19" s="50" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B20" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B22" s="50" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C22" s="128">
         <f>Data!C3</f>
@@ -2982,7 +2983,7 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B23" s="1" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="C23" s="87">
         <f>Normalized_FCF!C16</f>
@@ -2995,7 +2996,7 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B24" s="1" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="C24" s="87">
         <f>Normalized_FCF!C11</f>
@@ -3004,7 +3005,7 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B25" s="125" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C25" s="87">
         <f>C23+C24</f>
@@ -3013,7 +3014,7 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B27" s="1" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C27" s="87">
         <f>Normalized_FCF!C19</f>
@@ -3022,7 +3023,7 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B28" s="1" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="C28" s="124">
         <f>C27/(Common_Shares/Data!C3)</f>
@@ -3031,7 +3032,7 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B29" s="1" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="C29" s="107">
         <f>C28/Market_Price</f>
@@ -3040,22 +3041,22 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B31" s="51" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B32" s="51" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B33" s="51" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B34" s="51" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.35">
@@ -3064,12 +3065,12 @@
         <v>2.</v>
       </c>
       <c r="B36" s="50" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B37" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="C37" s="144">
         <v>0.1</v>
@@ -3080,12 +3081,12 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B39" s="16" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B40" s="125" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="C40" s="130">
         <v>0</v>
@@ -3096,18 +3097,18 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B41" s="125" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="C41" s="130">
         <v>0</v>
       </c>
       <c r="D41" s="129" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B42" s="125" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="C42" s="130">
         <v>0</v>
@@ -3115,7 +3116,7 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B43" s="80" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="C43" s="81">
         <f>SUM(C40:C42)</f>
@@ -3128,32 +3129,32 @@
         <v>3.</v>
       </c>
       <c r="B45" s="50" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B46" s="50" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B47" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B48" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B50" s="50" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B51" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.35">
@@ -3162,32 +3163,32 @@
         <v>4.</v>
       </c>
       <c r="B53" s="50" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B54" s="50" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B55" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B57" s="50" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B58" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B60" s="50" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.35">
@@ -3197,7 +3198,7 @@
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B62" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.35">
@@ -3212,13 +3213,13 @@
     </row>
     <row r="66" spans="1:3" ht="12.75" x14ac:dyDescent="0.35">
       <c r="B66" s="119" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="C66"/>
     </row>
     <row r="67" spans="1:3" ht="12.75" x14ac:dyDescent="0.35">
       <c r="B67" s="119" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="C67" s="174">
         <v>3</v>
@@ -3226,7 +3227,7 @@
     </row>
     <row r="68" spans="1:3" ht="12.75" x14ac:dyDescent="0.35">
       <c r="B68" s="119" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="C68" s="194">
         <v>0.2</v>
@@ -3234,21 +3235,21 @@
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B69" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C69" s="179">
         <f>Scenarios!F83</f>
-        <v>-2.984172155033904E-2</v>
+        <v>-7.9621249175738762E-2</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B71" s="50" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B72" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.35">
@@ -3257,37 +3258,37 @@
         <v>5.</v>
       </c>
       <c r="B74" s="50" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B75" s="50" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B76" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B78" s="50" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B79" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B80" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="82" spans="1:5" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A82" s="37" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B82" s="37"/>
       <c r="C82" s="37"/>
@@ -3296,21 +3297,21 @@
     </row>
     <row r="84" spans="1:5" ht="12.4" x14ac:dyDescent="0.4">
       <c r="B84" s="151" t="s">
+        <v>201</v>
+      </c>
+      <c r="C84" s="151" t="s">
+        <v>225</v>
+      </c>
+      <c r="D84" s="152" t="s">
+        <v>196</v>
+      </c>
+      <c r="E84" s="152" t="s">
         <v>204</v>
-      </c>
-      <c r="C84" s="151" t="s">
-        <v>229</v>
-      </c>
-      <c r="D84" s="152" t="s">
-        <v>199</v>
-      </c>
-      <c r="E84" s="152" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="85" spans="1:5" ht="12.75" x14ac:dyDescent="0.35">
       <c r="B85" s="150" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C85" s="165"/>
       <c r="D85" s="158"/>
@@ -3318,7 +3319,7 @@
     </row>
     <row r="86" spans="1:5" ht="12.75" x14ac:dyDescent="0.35">
       <c r="B86" s="150" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="C86" s="165"/>
       <c r="D86" s="158"/>
@@ -3326,7 +3327,7 @@
     </row>
     <row r="87" spans="1:5" ht="12.75" x14ac:dyDescent="0.35">
       <c r="B87" s="150" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="C87" s="165"/>
       <c r="D87" s="158"/>
@@ -3334,7 +3335,7 @@
     </row>
     <row r="88" spans="1:5" ht="12.75" x14ac:dyDescent="0.35">
       <c r="B88" s="150" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="C88" s="165"/>
       <c r="D88" s="158"/>
@@ -3342,11 +3343,11 @@
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B90" s="50" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C90" s="170">
         <f>Scenarios!C83</f>
-        <v>2.8713197359937066</v>
+        <v>3.120855461920689</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Reporting_currency</f>
@@ -3355,7 +3356,7 @@
     </row>
     <row r="92" spans="1:5" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A92" s="37" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B92" s="37"/>
       <c r="C92" s="37"/>
@@ -3364,32 +3365,32 @@
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B93" s="50" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B94" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B96" s="50" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="97" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B97" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="99" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B99" s="50" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="100" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B100" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
   </sheetData>
@@ -3483,7 +3484,7 @@
     </row>
     <row r="2" spans="2:13" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B2" s="37" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="C2" s="38"/>
       <c r="D2" s="38"/>
@@ -3539,7 +3540,7 @@
     </row>
     <row r="5" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B5" s="42" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C5" s="225">
         <v>86428</v>
@@ -3571,7 +3572,7 @@
     </row>
     <row r="6" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B6" s="42" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C6" s="225">
         <v>13300.2</v>
@@ -3603,7 +3604,7 @@
     </row>
     <row r="7" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B7" s="79" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C7" s="226">
         <v>9513.2000000000007</v>
@@ -3623,7 +3624,7 @@
     </row>
     <row r="8" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B8" s="42" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C8" s="225"/>
       <c r="D8" s="216"/>
@@ -3639,7 +3640,7 @@
     </row>
     <row r="9" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B9" s="42" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="C9" s="225"/>
       <c r="D9" s="216"/>
@@ -3655,7 +3656,7 @@
     </row>
     <row r="10" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B10" s="42" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="C10" s="225"/>
       <c r="D10" s="216"/>
@@ -3671,7 +3672,7 @@
     </row>
     <row r="11" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B11" s="42" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="C11" s="225"/>
       <c r="D11" s="216"/>
@@ -3687,7 +3688,7 @@
     </row>
     <row r="12" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B12" s="42" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C12" s="225">
         <v>704.6</v>
@@ -3719,7 +3720,7 @@
     </row>
     <row r="13" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B13" s="42" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C13" s="225">
         <v>183.1</v>
@@ -3739,7 +3740,7 @@
     </row>
     <row r="14" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B14" s="42" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C14" s="225"/>
       <c r="D14" s="216"/>
@@ -3755,7 +3756,7 @@
     </row>
     <row r="15" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B15" s="45" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C15" s="227"/>
       <c r="D15" s="217">
@@ -3785,7 +3786,7 @@
     </row>
     <row r="16" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B16" s="29" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C16" s="225">
         <v>107.9</v>
@@ -3817,13 +3818,13 @@
     </row>
     <row r="18" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B18" s="16" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C18" s="9"/>
     </row>
     <row r="19" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B19" s="28" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C19" s="216"/>
       <c r="D19" s="216"/>
@@ -3839,7 +3840,7 @@
     </row>
     <row r="20" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B20" s="28" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C20" s="216"/>
       <c r="D20" s="216"/>
@@ -3855,7 +3856,7 @@
     </row>
     <row r="21" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B21" s="28" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C21" s="216"/>
       <c r="D21" s="216"/>
@@ -3940,7 +3941,7 @@
     </row>
     <row r="27" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B27" s="30" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C27" s="217">
         <v>60481</v>
@@ -3988,7 +3989,7 @@
     </row>
     <row r="29" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B29" s="27" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="C29" s="216">
         <v>1036.4000000000001</v>
@@ -4012,13 +4013,13 @@
     </row>
     <row r="31" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B31" s="16" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C31" s="9"/>
     </row>
     <row r="32" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B32" s="27" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C32" s="216"/>
       <c r="D32" s="216"/>
@@ -4034,7 +4035,7 @@
     </row>
     <row r="34" spans="2:13" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B34" s="37" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C34" s="38"/>
       <c r="D34" s="38"/>
@@ -4104,7 +4105,7 @@
     </row>
     <row r="37" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B37" s="42" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C37" s="218">
         <f t="shared" ref="C37:M37" si="2">IF(C$4="","",-C5)</f>
@@ -4153,7 +4154,7 @@
     </row>
     <row r="38" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B38" s="32" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C38" s="219">
         <f>IF(C36="","",C36+C37)</f>
@@ -4202,7 +4203,7 @@
     </row>
     <row r="39" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B39" s="42" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C39" s="218">
         <f t="shared" ref="C39:M39" si="13">IF(C$4="","",-C6)</f>
@@ -4251,7 +4252,7 @@
     </row>
     <row r="40" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B40" s="79" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C40" s="220">
         <f t="shared" ref="C40:M40" si="14">IF(C$4="","",-C7)</f>
@@ -4300,7 +4301,7 @@
     </row>
     <row r="41" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B41" s="79" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C41" s="220">
         <f>IF(C$4="","",C39-C40)</f>
@@ -4349,7 +4350,7 @@
     </row>
     <row r="42" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B42" s="42" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C42" s="218">
         <f t="shared" ref="C42:M42" si="16">IF(C$4="","",-C8)</f>
@@ -4398,7 +4399,7 @@
     </row>
     <row r="43" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B43" s="45" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="C43" s="221">
         <f>IF(C$4="","",C38+C39+C42)</f>
@@ -4447,7 +4448,7 @@
     </row>
     <row r="44" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B44" s="45" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="C44" s="222">
         <f t="shared" ref="C44:M44" si="18">IF(C$4="","",C47-C46-C45-C43)</f>
@@ -4496,7 +4497,7 @@
     </row>
     <row r="45" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B45" s="42" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C45" s="223">
         <f t="shared" ref="C45:M45" si="19">IF(C$4="","",C51+C52)</f>
@@ -4545,7 +4546,7 @@
     </row>
     <row r="46" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B46" s="42" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C46" s="218">
         <f t="shared" ref="C46:M46" si="20">IF(C$4="","",-C14)</f>
@@ -4594,7 +4595,7 @@
     </row>
     <row r="47" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B47" s="45" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C47" s="221">
         <f t="shared" ref="C47:M47" si="21">IF(C$4="","",C15)</f>
@@ -4643,7 +4644,7 @@
     </row>
     <row r="48" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B48" s="29" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C48" s="218">
         <f t="shared" ref="C48:M48" si="22">IF(C$4="","",MIN(-C16,0))</f>
@@ -4692,12 +4693,12 @@
     </row>
     <row r="50" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B50" s="16" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="51" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B51" s="42" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C51" s="218">
         <f t="shared" ref="C51:M51" si="23">IF(C$4="","",-C12)</f>
@@ -4746,7 +4747,7 @@
     </row>
     <row r="52" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B52" s="42" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C52" s="218">
         <f t="shared" ref="C52:M52" si="24">IF(C$4="","",C13)</f>
@@ -4795,12 +4796,12 @@
     </row>
     <row r="54" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B54" s="210" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
     </row>
     <row r="55" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B55" s="42" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="C55" s="87">
         <f t="shared" ref="C55:M55" si="25">IF(C$4="","",C9)</f>
@@ -4849,7 +4850,7 @@
     </row>
     <row r="56" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B56" s="42" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="C56" s="87">
         <f t="shared" ref="C56:M56" si="26">IF(C$4="","",C10)</f>
@@ -4898,7 +4899,7 @@
     </row>
     <row r="57" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B57" s="42" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="C57" s="87">
         <f>IF(C$4="","",C11)</f>
@@ -4947,7 +4948,7 @@
     </row>
     <row r="58" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B58" s="42" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="C58" s="87">
         <f>IF(C$4="","",C44-C55-C56-C57)</f>
@@ -4996,13 +4997,13 @@
     </row>
     <row r="60" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B60" s="16" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C60" s="9"/>
     </row>
     <row r="61" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B61" s="28" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C61" s="63">
         <f t="shared" ref="C61:M61" si="29">IF(C$4="","",-C19)</f>
@@ -5051,7 +5052,7 @@
     </row>
     <row r="62" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B62" s="28" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C62" s="63">
         <f t="shared" ref="C62:M62" si="30">IF(C$4="","",-C20)</f>
@@ -5100,7 +5101,7 @@
     </row>
     <row r="63" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B63" s="28" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C63" s="63">
         <f t="shared" ref="C63:M63" si="31">IF(C$4="","",-C21)</f>
@@ -5198,7 +5199,7 @@
     </row>
     <row r="66" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B66" s="105" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="67" spans="2:13" x14ac:dyDescent="0.35">
@@ -5453,7 +5454,7 @@
     </row>
     <row r="73" spans="2:13" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B73" s="37" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C73" s="38"/>
       <c r="D73" s="38"/>
@@ -5524,7 +5525,7 @@
     </row>
     <row r="76" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B76" s="110" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C76" s="83">
         <f t="shared" ref="C76:H77" si="39">IF(C$4="","",C25)</f>
@@ -5558,7 +5559,7 @@
     </row>
     <row r="77" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B77" s="110" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C77" s="83">
         <f t="shared" si="39"/>
@@ -5592,7 +5593,7 @@
     </row>
     <row r="78" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B78" s="27" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C78" s="63">
         <f t="shared" ref="C78:M78" si="40">IF(C$4="","",C27)</f>
@@ -5719,7 +5720,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q799"/>
+  <dimension ref="A1:Q802"/>
   <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="1.33203125" style="2" customWidth="1"/>
@@ -5739,7 +5740,7 @@
         <v>HKD</v>
       </c>
       <c r="C1" s="58" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D1" s="58"/>
       <c r="E1" s="58"/>
@@ -5792,12 +5793,12 @@
     <row r="2" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A2" s="3"/>
       <c r="B2" s="59" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="C2" s="59"/>
       <c r="D2" s="61"/>
       <c r="E2" s="72" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F2" s="61"/>
       <c r="G2" s="38"/>
@@ -5815,7 +5816,7 @@
     <row r="3" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="10"/>
       <c r="B3" s="16" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="C3" s="127">
         <f>Data!C3</f>
@@ -5885,7 +5886,7 @@
     <row r="5" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="10"/>
       <c r="B5" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C5" s="229">
         <f>C25</f>
@@ -5893,54 +5894,54 @@
       </c>
       <c r="E5" s="18"/>
       <c r="G5" s="218">
-        <f>G25</f>
+        <f t="shared" ref="G5:Q5" si="1">G25</f>
         <v>-95941.2</v>
       </c>
       <c r="H5" s="218">
-        <f>H25</f>
+        <f t="shared" si="1"/>
         <v>-83487.199999999997</v>
       </c>
       <c r="I5" s="218">
-        <f>I25</f>
+        <f t="shared" si="1"/>
         <v>-76598</v>
       </c>
       <c r="J5" s="218">
-        <f>J25</f>
+        <f t="shared" si="1"/>
         <v>-50089.1</v>
       </c>
       <c r="K5" s="218">
-        <f>K25</f>
+        <f t="shared" si="1"/>
         <v>-40654.6</v>
       </c>
       <c r="L5" s="218">
-        <f>L25</f>
+        <f t="shared" si="1"/>
         <v>-48059.1</v>
       </c>
       <c r="M5" s="218">
-        <f>M25</f>
+        <f t="shared" si="1"/>
         <v>-42943</v>
       </c>
       <c r="N5" s="218">
-        <f>N25</f>
+        <f t="shared" si="1"/>
         <v>-36282.800000000003</v>
       </c>
       <c r="O5" s="218" t="str">
-        <f>O25</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="P5" s="218" t="str">
-        <f>P25</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="Q5" s="218" t="str">
-        <f>Q25</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="6" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="10"/>
       <c r="B6" s="32" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C6" s="219">
         <f>C4+C5</f>
@@ -5952,50 +5953,50 @@
         <v>12771.800000000003</v>
       </c>
       <c r="H6" s="219">
-        <f t="shared" ref="H6:Q6" si="1">IF(H4="","",H4+H5)</f>
+        <f t="shared" ref="H6:Q6" si="2">IF(H4="","",H4+H5)</f>
         <v>11197.199999999997</v>
       </c>
       <c r="I6" s="219">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>22339.699999999997</v>
       </c>
       <c r="J6" s="219">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>20074.700000000004</v>
       </c>
       <c r="K6" s="219">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>16096.200000000004</v>
       </c>
       <c r="L6" s="219">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>18601.799999999996</v>
       </c>
       <c r="M6" s="219">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>16213.400000000001</v>
       </c>
       <c r="N6" s="219">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>14962.699999999997</v>
       </c>
       <c r="O6" s="219" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="P6" s="219" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="Q6" s="219" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="7" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="10"/>
       <c r="B7" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C7" s="229">
         <f>C35</f>
@@ -6003,54 +6004,54 @@
       </c>
       <c r="E7" s="18"/>
       <c r="G7" s="229">
-        <f>G35</f>
+        <f t="shared" ref="G7:Q7" si="3">G35</f>
         <v>-3787</v>
       </c>
       <c r="H7" s="229">
-        <f>H35</f>
+        <f t="shared" si="3"/>
         <v>-3721.3999999999996</v>
       </c>
       <c r="I7" s="229">
-        <f>I35</f>
+        <f t="shared" si="3"/>
         <v>-14003.8</v>
       </c>
       <c r="J7" s="229">
-        <f>J35</f>
+        <f t="shared" si="3"/>
         <v>-11888.399999999998</v>
       </c>
       <c r="K7" s="229">
-        <f>K35</f>
+        <f t="shared" si="3"/>
         <v>-11596.6</v>
       </c>
       <c r="L7" s="229">
-        <f>L35</f>
+        <f t="shared" si="3"/>
         <v>-12064.3</v>
       </c>
       <c r="M7" s="229">
-        <f>M35</f>
+        <f t="shared" si="3"/>
         <v>-10960.1</v>
       </c>
       <c r="N7" s="229">
-        <f>N35</f>
+        <f t="shared" si="3"/>
         <v>-10347.099999999999</v>
       </c>
       <c r="O7" s="229" t="str">
-        <f>O35</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="P7" s="229" t="str">
-        <f>P35</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="Q7" s="229" t="str">
-        <f>Q35</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="8" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="10"/>
       <c r="B8" s="30" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="C8" s="230">
         <f>C6+C7</f>
@@ -6064,50 +6065,50 @@
         <v>8984.8000000000029</v>
       </c>
       <c r="H8" s="219">
-        <f t="shared" ref="H8:Q8" si="2">IF(H$4="","",H6+H7)</f>
+        <f t="shared" ref="H8:Q8" si="4">IF(H$4="","",H6+H7)</f>
         <v>7475.7999999999975</v>
       </c>
       <c r="I8" s="219">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>8335.8999999999978</v>
       </c>
       <c r="J8" s="219">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>8186.3000000000065</v>
       </c>
       <c r="K8" s="219">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>4499.600000000004</v>
       </c>
       <c r="L8" s="219">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>6537.4999999999964</v>
       </c>
       <c r="M8" s="219">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>5253.3000000000011</v>
       </c>
       <c r="N8" s="219">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>4615.5999999999985</v>
       </c>
       <c r="O8" s="219" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="P8" s="219" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="Q8" s="219" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="9" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="10"/>
       <c r="B9" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C9" s="229">
         <f>BS!$G$39*BS!D59</f>
@@ -6162,7 +6163,7 @@
     <row r="10" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="10"/>
       <c r="B10" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C10" s="229">
         <f>-C4*C77</f>
@@ -6217,7 +6218,7 @@
     <row r="11" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="10"/>
       <c r="B11" s="32" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="C11" s="231">
         <f>C62</f>
@@ -6225,7 +6226,7 @@
       </c>
       <c r="D11" s="201"/>
       <c r="E11" s="76" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="F11" s="201"/>
       <c r="G11" s="221">
@@ -6233,50 +6234,50 @@
         <v>-8463.2999999999993</v>
       </c>
       <c r="H11" s="221">
-        <f t="shared" ref="H11:Q11" si="3">H62</f>
+        <f t="shared" ref="H11:Q11" si="5">H62</f>
         <v>-7013.1000000000013</v>
       </c>
       <c r="I11" s="221">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>-7830.5999999999976</v>
       </c>
       <c r="J11" s="221">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>-7660.6000000000067</v>
       </c>
       <c r="K11" s="221">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>-3857.9000000000042</v>
       </c>
       <c r="L11" s="221">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>-6059.9999999999964</v>
       </c>
       <c r="M11" s="221">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>-4901.2000000000007</v>
       </c>
       <c r="N11" s="221">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>-4283.1999999999989</v>
       </c>
       <c r="O11" s="221" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="P11" s="221" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="Q11" s="221" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="12" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="10"/>
       <c r="B12" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C12" s="229">
         <f>C49</f>
@@ -6284,54 +6285,54 @@
       </c>
       <c r="E12" s="18"/>
       <c r="G12" s="229">
-        <f>G49</f>
+        <f t="shared" ref="G12:Q12" si="6">G49</f>
         <v>-521.5</v>
       </c>
       <c r="H12" s="229">
-        <f>H49</f>
+        <f t="shared" si="6"/>
         <v>-357.59999999999997</v>
       </c>
       <c r="I12" s="229">
-        <f>I49</f>
+        <f t="shared" si="6"/>
         <v>-337.7</v>
       </c>
       <c r="J12" s="229">
-        <f>J49</f>
+        <f t="shared" si="6"/>
         <v>-376</v>
       </c>
       <c r="K12" s="229">
-        <f>K49</f>
+        <f t="shared" si="6"/>
         <v>-559.6</v>
       </c>
       <c r="L12" s="229">
-        <f>L49</f>
+        <f t="shared" si="6"/>
         <v>-370.3</v>
       </c>
       <c r="M12" s="229">
-        <f>M49</f>
+        <f t="shared" si="6"/>
         <v>-243.7</v>
       </c>
       <c r="N12" s="229">
-        <f>N49</f>
+        <f t="shared" si="6"/>
         <v>-236.6</v>
       </c>
       <c r="O12" s="229" t="str">
-        <f>O49</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="P12" s="229" t="str">
-        <f>P49</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="Q12" s="229" t="str">
-        <f>Q49</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="13" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="10"/>
       <c r="B13" s="80" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="C13" s="219">
         <f>SUM(C8:C12)</f>
@@ -6343,50 +6344,50 @@
         <v>3.637978807091713E-12</v>
       </c>
       <c r="H13" s="219">
-        <f t="shared" ref="H13:Q13" si="4">IF(H$4="","",SUM(H8:H12))</f>
+        <f t="shared" ref="H13:Q13" si="7">IF(H$4="","",SUM(H8:H12))</f>
         <v>105.09999999999621</v>
       </c>
       <c r="I13" s="219">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>167.60000000000019</v>
       </c>
       <c r="J13" s="219">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>149.69999999999982</v>
       </c>
       <c r="K13" s="219">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>82.099999999999795</v>
       </c>
       <c r="L13" s="219">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>107.19999999999999</v>
       </c>
       <c r="M13" s="219">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>108.40000000000038</v>
       </c>
       <c r="N13" s="219">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>95.799999999999642</v>
       </c>
       <c r="O13" s="219" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="P13" s="219" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="Q13" s="219" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="14" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="10"/>
       <c r="B14" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C14" s="229">
         <f>-C13*C43</f>
@@ -6441,10 +6442,10 @@
     <row r="15" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="10"/>
       <c r="B15" s="42" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C15" s="229">
-        <f>-C4*C81</f>
+        <f>-C4*C82</f>
         <v>-215.01859206599408</v>
       </c>
       <c r="D15" s="66"/>
@@ -6498,7 +6499,7 @@
     <row r="16" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="10"/>
       <c r="B16" s="43" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C16" s="232">
         <f>SUM(C13:C15)</f>
@@ -6512,58 +6513,58 @@
         <v>-107.89999999999637</v>
       </c>
       <c r="H16" s="219">
-        <f t="shared" ref="H16:Q16" si="5">IF(H$4="","",SUM(H13:H15))</f>
+        <f t="shared" ref="H16:Q16" si="8">IF(H$4="","",SUM(H13:H15))</f>
         <v>-3.780087354243733E-12</v>
       </c>
       <c r="I16" s="219">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J16" s="219">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="K16" s="219">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>-1.9895196601282805E-13</v>
       </c>
       <c r="L16" s="219">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="M16" s="219">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>3.694822225952521E-13</v>
       </c>
       <c r="N16" s="219">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>-3.5527136788005009E-13</v>
       </c>
       <c r="O16" s="219" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="P16" s="219" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="Q16" s="219" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
     <row r="17" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="10"/>
       <c r="B17" s="28" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C17" s="229">
-        <f>-C4*C83</f>
+        <f>-C4*C84</f>
         <v>0</v>
       </c>
       <c r="D17" s="64"/>
       <c r="E17" s="76" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="F17" s="64"/>
       <c r="G17" s="233"/>
@@ -6581,15 +6582,15 @@
     <row r="18" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="10"/>
       <c r="B18" s="28" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="C18" s="229">
-        <f>-C4*C84</f>
+        <f>-C4*C85</f>
         <v>0</v>
       </c>
       <c r="D18" s="64"/>
       <c r="E18" s="76" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="F18" s="64"/>
       <c r="G18" s="234"/>
@@ -6607,7 +6608,7 @@
     <row r="19" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="10"/>
       <c r="B19" s="32" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="C19" s="219">
         <f>SUM(C16:C18)</f>
@@ -6617,47 +6618,47 @@
       <c r="E19" s="77"/>
       <c r="F19" s="28"/>
       <c r="G19" s="221">
-        <f t="shared" ref="G19:Q19" si="6">IF(G$4="","",SUM(G16:G18))</f>
+        <f t="shared" ref="G19:Q19" si="9">IF(G$4="","",SUM(G16:G18))</f>
         <v>-107.89999999999637</v>
       </c>
       <c r="H19" s="221">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>-3.780087354243733E-12</v>
       </c>
       <c r="I19" s="221">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="J19" s="221">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="K19" s="221">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>-1.9895196601282805E-13</v>
       </c>
       <c r="L19" s="221">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="M19" s="221">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>3.694822225952521E-13</v>
       </c>
       <c r="N19" s="221">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>-3.5527136788005009E-13</v>
       </c>
       <c r="O19" s="221" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="P19" s="221" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="Q19" s="221" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -6683,12 +6684,12 @@
     <row r="21" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A21" s="10"/>
       <c r="B21" s="59" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="C21" s="59"/>
       <c r="D21" s="61"/>
       <c r="E21" s="72" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F21" s="61"/>
       <c r="G21" s="38"/>
@@ -6706,7 +6707,7 @@
     <row r="22" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="10"/>
       <c r="B22" s="70" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C22" s="68"/>
       <c r="D22" s="28"/>
@@ -6727,7 +6728,7 @@
     <row r="23" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="10"/>
       <c r="B23" s="28" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C23" s="235">
         <f>-C4*C28</f>
@@ -6784,7 +6785,7 @@
     <row r="24" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="10"/>
       <c r="B24" s="78" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C24" s="229">
         <f>-C4*C29</f>
@@ -6841,7 +6842,7 @@
     <row r="25" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="10"/>
       <c r="B25" s="80" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C25" s="219">
         <f>C23+C24</f>
@@ -6851,47 +6852,47 @@
       <c r="E25" s="73"/>
       <c r="F25" s="9"/>
       <c r="G25" s="219">
-        <f>IF(G$4="","",G23+G24)</f>
+        <f t="shared" ref="G25:Q25" si="10">IF(G$4="","",G23+G24)</f>
         <v>-95941.2</v>
       </c>
       <c r="H25" s="219">
-        <f>IF(H$4="","",H23+H24)</f>
+        <f t="shared" si="10"/>
         <v>-83487.199999999997</v>
       </c>
       <c r="I25" s="219">
-        <f>IF(I$4="","",I23+I24)</f>
+        <f t="shared" si="10"/>
         <v>-76598</v>
       </c>
       <c r="J25" s="219">
-        <f>IF(J$4="","",J23+J24)</f>
+        <f t="shared" si="10"/>
         <v>-50089.1</v>
       </c>
       <c r="K25" s="219">
-        <f>IF(K$4="","",K23+K24)</f>
+        <f t="shared" si="10"/>
         <v>-40654.6</v>
       </c>
       <c r="L25" s="219">
-        <f>IF(L$4="","",L23+L24)</f>
+        <f t="shared" si="10"/>
         <v>-48059.1</v>
       </c>
       <c r="M25" s="219">
-        <f>IF(M$4="","",M23+M24)</f>
+        <f t="shared" si="10"/>
         <v>-42943</v>
       </c>
       <c r="N25" s="219">
-        <f>IF(N$4="","",N23+N24)</f>
+        <f t="shared" si="10"/>
         <v>-36282.800000000003</v>
       </c>
       <c r="O25" s="219" t="str">
-        <f>IF(O$4="","",O23+O24)</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="P25" s="219" t="str">
-        <f>IF(P$4="","",P23+P24)</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="Q25" s="219" t="str">
-        <f>IF(Q$4="","",Q23+Q24)</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -6901,13 +6902,13 @@
     <row r="27" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="10"/>
       <c r="B27" s="70" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
     </row>
     <row r="28" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="10"/>
       <c r="B28" s="27" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C28" s="69">
         <f>AVERAGE(G28:H28)</f>
@@ -6915,51 +6916,51 @@
       </c>
       <c r="D28" s="27"/>
       <c r="E28" s="74" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F28" s="27"/>
       <c r="G28" s="13">
-        <f>IF(G$4="","",ABS(G23/G$4))</f>
+        <f t="shared" ref="G28:Q28" si="11">IF(G$4="","",ABS(G23/G$4))</f>
         <v>0.79501071628968012</v>
       </c>
       <c r="H28" s="13">
-        <f>IF(H$4="","",ABS(H23/H$4))</f>
+        <f t="shared" si="11"/>
         <v>0.77639928013484794</v>
       </c>
       <c r="I28" s="13">
-        <f>IF(I$4="","",ABS(I23/I$4))</f>
+        <f t="shared" si="11"/>
         <v>0.77420437305496292</v>
       </c>
       <c r="J28" s="13">
-        <f>IF(J$4="","",ABS(J23/J$4))</f>
+        <f t="shared" si="11"/>
         <v>0.71388807333696291</v>
       </c>
       <c r="K28" s="13">
-        <f>IF(K$4="","",ABS(K23/K$4))</f>
+        <f t="shared" si="11"/>
         <v>0.71637051812485453</v>
       </c>
       <c r="L28" s="13">
-        <f>IF(L$4="","",ABS(L23/L$4))</f>
+        <f t="shared" si="11"/>
         <v>0.72094886207656972</v>
       </c>
       <c r="M28" s="13">
-        <f>IF(M$4="","",ABS(M23/M$4))</f>
+        <f t="shared" si="11"/>
         <v>0.72592314610084452</v>
       </c>
       <c r="N28" s="13">
-        <f>IF(N$4="","",ABS(N23/N$4))</f>
+        <f t="shared" si="11"/>
         <v>0.70801924071381883</v>
       </c>
       <c r="O28" s="13" t="str">
-        <f>IF(O$4="","",ABS(O23/O$4))</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="P28" s="13" t="str">
-        <f>IF(P$4="","",ABS(P23/P$4))</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="Q28" s="13" t="str">
-        <f>IF(Q$4="","",ABS(Q23/Q$4))</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -6975,105 +6976,105 @@
       </c>
       <c r="D29" s="27"/>
       <c r="E29" s="74" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F29" s="27"/>
       <c r="G29" s="13">
-        <f>IF(G$4="","",ABS(G24/G$4))</f>
+        <f t="shared" ref="G29:Q29" si="12">IF(G$4="","",ABS(G24/G$4))</f>
         <v>8.750747380718038E-2</v>
       </c>
       <c r="H29" s="13">
-        <f>IF(H$4="","",ABS(H24/H$4))</f>
+        <f t="shared" si="12"/>
         <v>0.10534259075412634</v>
       </c>
       <c r="I29" s="13">
-        <f>IF(I$4="","",ABS(I24/I$4))</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="J29" s="13">
-        <f>IF(J$4="","",ABS(J24/J$4))</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="K29" s="13">
-        <f>IF(K$4="","",ABS(K24/K$4))</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="L29" s="13">
-        <f>IF(L$4="","",ABS(L24/L$4))</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="M29" s="13">
-        <f>IF(M$4="","",ABS(M24/M$4))</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="N29" s="13">
-        <f>IF(N$4="","",ABS(N24/N$4))</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="O29" s="13" t="str">
-        <f>IF(O$4="","",ABS(O24/O$4))</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="P29" s="13" t="str">
-        <f>IF(P$4="","",ABS(P24/P$4))</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="Q29" s="13" t="str">
-        <f>IF(Q$4="","",ABS(Q24/Q$4))</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="30" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="10"/>
       <c r="B30" s="80" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C30" s="81">
         <f>ABS(C25/$C$4)</f>
         <v>0.88213003049291738</v>
       </c>
       <c r="G30" s="31">
-        <f>IF(G$4="","",ABS(G25/G$4))</f>
+        <f t="shared" ref="G30:Q30" si="13">IF(G$4="","",ABS(G25/G$4))</f>
         <v>0.8825181900968605</v>
       </c>
       <c r="H30" s="31">
-        <f>IF(H$4="","",ABS(H25/H$4))</f>
+        <f t="shared" si="13"/>
         <v>0.88174187088897438</v>
       </c>
       <c r="I30" s="31">
-        <f>IF(I$4="","",ABS(I25/I$4))</f>
+        <f t="shared" si="13"/>
         <v>0.77420437305496292</v>
       </c>
       <c r="J30" s="31">
-        <f>IF(J$4="","",ABS(J25/J$4))</f>
+        <f t="shared" si="13"/>
         <v>0.71388807333696291</v>
       </c>
       <c r="K30" s="31">
-        <f>IF(K$4="","",ABS(K25/K$4))</f>
+        <f t="shared" si="13"/>
         <v>0.71637051812485453</v>
       </c>
       <c r="L30" s="31">
-        <f>IF(L$4="","",ABS(L25/L$4))</f>
+        <f t="shared" si="13"/>
         <v>0.72094886207656972</v>
       </c>
       <c r="M30" s="31">
-        <f>IF(M$4="","",ABS(M25/M$4))</f>
+        <f t="shared" si="13"/>
         <v>0.72592314610084452</v>
       </c>
       <c r="N30" s="31">
-        <f>IF(N$4="","",ABS(N25/N$4))</f>
+        <f t="shared" si="13"/>
         <v>0.70801924071381883</v>
       </c>
       <c r="O30" s="31" t="str">
-        <f>IF(O$4="","",ABS(O25/O$4))</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="P30" s="31" t="str">
-        <f>IF(P$4="","",ABS(P25/P$4))</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="Q30" s="31" t="str">
-        <f>IF(Q$4="","",ABS(Q25/Q$4))</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -7083,20 +7084,20 @@
     <row r="32" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="10"/>
       <c r="B32" s="70" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="33" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="10"/>
       <c r="B33" s="8" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="C33" s="236">
         <f>AVERAGE(G33:H33)</f>
         <v>-3754.2</v>
       </c>
       <c r="E33" s="74" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G33" s="229">
         <f>Data!C41</f>
@@ -7146,7 +7147,7 @@
     <row r="34" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="10"/>
       <c r="B34" s="28" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C34" s="236">
         <f>AVERAGE(G34:J34)</f>
@@ -7154,7 +7155,7 @@
       </c>
       <c r="D34" s="64"/>
       <c r="E34" s="74" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F34" s="64"/>
       <c r="G34" s="218">
@@ -7205,7 +7206,7 @@
     <row r="35" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="10"/>
       <c r="B35" s="80" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C35" s="219">
         <f>C33+C34</f>
@@ -7215,47 +7216,47 @@
       <c r="E35" s="76"/>
       <c r="F35" s="64"/>
       <c r="G35" s="219">
-        <f>IF(G4="","",G33+G34)</f>
+        <f t="shared" ref="G35:Q35" si="14">IF(G4="","",G33+G34)</f>
         <v>-3787</v>
       </c>
       <c r="H35" s="219">
-        <f>IF(H4="","",H33+H34)</f>
+        <f t="shared" si="14"/>
         <v>-3721.3999999999996</v>
       </c>
       <c r="I35" s="219">
-        <f>IF(I4="","",I33+I34)</f>
+        <f t="shared" si="14"/>
         <v>-14003.8</v>
       </c>
       <c r="J35" s="219">
-        <f>IF(J4="","",J33+J34)</f>
+        <f t="shared" si="14"/>
         <v>-11888.399999999998</v>
       </c>
       <c r="K35" s="219">
-        <f>IF(K4="","",K33+K34)</f>
+        <f t="shared" si="14"/>
         <v>-11596.6</v>
       </c>
       <c r="L35" s="219">
-        <f>IF(L4="","",L33+L34)</f>
+        <f t="shared" si="14"/>
         <v>-12064.3</v>
       </c>
       <c r="M35" s="219">
-        <f>IF(M4="","",M33+M34)</f>
+        <f t="shared" si="14"/>
         <v>-10960.1</v>
       </c>
       <c r="N35" s="219">
-        <f>IF(N4="","",N33+N34)</f>
+        <f t="shared" si="14"/>
         <v>-10347.099999999999</v>
       </c>
       <c r="O35" s="219" t="str">
-        <f>IF(O4="","",O33+O34)</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="P35" s="219" t="str">
-        <f>IF(P4="","",P33+P34)</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="Q35" s="219" t="str">
-        <f>IF(Q4="","",Q33+Q34)</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -7265,7 +7266,7 @@
     <row r="37" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="10"/>
       <c r="B37" s="70" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
     </row>
     <row r="38" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -7282,47 +7283,47 @@
       <c r="E38" s="28"/>
       <c r="F38" s="28"/>
       <c r="G38" s="13">
-        <f>IF(G$4="","",ABS(G33/G$4))</f>
+        <f t="shared" ref="G38:Q38" si="15">IF(G$4="","",ABS(G33/G$4))</f>
         <v>3.4834840359478626E-2</v>
       </c>
       <c r="H38" s="13">
-        <f>IF(H$4="","",ABS(H33/H$4))</f>
+        <f t="shared" si="15"/>
         <v>3.9303200949681254E-2</v>
       </c>
       <c r="I38" s="13">
-        <f>IF(I$4="","",ABS(I33/I$4))</f>
+        <f t="shared" si="15"/>
         <v>0.14154159637832697</v>
       </c>
       <c r="J38" s="13">
-        <f>IF(J$4="","",ABS(J33/J$4))</f>
+        <f t="shared" si="15"/>
         <v>0.16943780125933883</v>
       </c>
       <c r="K38" s="13">
-        <f>IF(K$4="","",ABS(K33/K$4))</f>
+        <f t="shared" si="15"/>
         <v>0.20434249385030695</v>
       </c>
       <c r="L38" s="13">
-        <f>IF(L$4="","",ABS(L33/L$4))</f>
+        <f t="shared" si="15"/>
         <v>0.18098015478338877</v>
       </c>
       <c r="M38" s="13">
-        <f>IF(M$4="","",ABS(M33/M$4))</f>
+        <f t="shared" si="15"/>
         <v>0.18527327558810205</v>
       </c>
       <c r="N38" s="13">
-        <f>IF(N$4="","",ABS(N33/N$4))</f>
+        <f t="shared" si="15"/>
         <v>0.20191236303675442</v>
       </c>
       <c r="O38" s="13" t="str">
-        <f>IF(O$4="","",ABS(O33/O$4))</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="P38" s="13" t="str">
-        <f>IF(P$4="","",ABS(P33/P$4))</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="Q38" s="13" t="str">
-        <f>IF(Q$4="","",ABS(Q33/Q$4))</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -7340,101 +7341,101 @@
       <c r="E39" s="28"/>
       <c r="F39" s="28"/>
       <c r="G39" s="13">
-        <f>IF(G$4="","",ABS(G34/G$4))</f>
+        <f t="shared" ref="G39:Q39" si="16">IF(G$4="","",ABS(G34/G$4))</f>
         <v>0</v>
       </c>
       <c r="H39" s="13">
-        <f>IF(H$4="","",ABS(H34/H$4))</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="I39" s="13">
-        <f>IF(I$4="","",ABS(I34/I$4))</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="J39" s="13">
-        <f>IF(J$4="","",ABS(J34/J$4))</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="K39" s="13">
-        <f>IF(K$4="","",ABS(K34/K$4))</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="L39" s="13">
-        <f>IF(L$4="","",ABS(L34/L$4))</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="M39" s="13">
-        <f>IF(M$4="","",ABS(M34/M$4))</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="N39" s="13">
-        <f>IF(N$4="","",ABS(N34/N$4))</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="O39" s="13" t="str">
-        <f>IF(O$4="","",ABS(O34/O$4))</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="P39" s="13" t="str">
-        <f>IF(P$4="","",ABS(P34/P$4))</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="Q39" s="13" t="str">
-        <f>IF(Q$4="","",ABS(Q34/Q$4))</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="40" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="10"/>
       <c r="B40" s="80" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C40" s="81">
         <f>ABS(C35/$C$4)</f>
         <v>3.7252042518384404E-2</v>
       </c>
       <c r="G40" s="31">
-        <f>IF(G$4="","",ABS(G35/G$4))</f>
+        <f t="shared" ref="G40:Q40" si="17">IF(G$4="","",ABS(G35/G$4))</f>
         <v>3.4834840359478626E-2</v>
       </c>
       <c r="H40" s="31">
-        <f>IF(H$4="","",ABS(H35/H$4))</f>
+        <f t="shared" si="17"/>
         <v>3.9303200949681254E-2</v>
       </c>
       <c r="I40" s="31">
-        <f>IF(I$4="","",ABS(I35/I$4))</f>
+        <f t="shared" si="17"/>
         <v>0.14154159637832697</v>
       </c>
       <c r="J40" s="31">
-        <f>IF(J$4="","",ABS(J35/J$4))</f>
+        <f t="shared" si="17"/>
         <v>0.16943780125933883</v>
       </c>
       <c r="K40" s="31">
-        <f>IF(K$4="","",ABS(K35/K$4))</f>
+        <f t="shared" si="17"/>
         <v>0.20434249385030695</v>
       </c>
       <c r="L40" s="31">
-        <f>IF(L$4="","",ABS(L35/L$4))</f>
+        <f t="shared" si="17"/>
         <v>0.18098015478338877</v>
       </c>
       <c r="M40" s="31">
-        <f>IF(M$4="","",ABS(M35/M$4))</f>
+        <f t="shared" si="17"/>
         <v>0.18527327558810205</v>
       </c>
       <c r="N40" s="31">
-        <f>IF(N$4="","",ABS(N35/N$4))</f>
+        <f t="shared" si="17"/>
         <v>0.20191236303675442</v>
       </c>
       <c r="O40" s="31" t="str">
-        <f>IF(O$4="","",ABS(O35/O$4))</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="P40" s="31" t="str">
-        <f>IF(P$4="","",ABS(P35/P$4))</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="Q40" s="31" t="str">
-        <f>IF(Q$4="","",ABS(Q35/Q$4))</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -7444,64 +7445,64 @@
     <row r="42" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="10"/>
       <c r="B42" s="70" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
     </row>
     <row r="43" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="10"/>
       <c r="B43" s="28" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="C43" s="69">
         <v>0.23</v>
       </c>
       <c r="D43" s="28"/>
       <c r="E43" s="77" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F43" s="28"/>
       <c r="G43" s="6">
-        <f>IF(G$4="","",-G14/G16)</f>
+        <f t="shared" ref="G43:Q43" si="18">IF(G$4="","",-G14/G16)</f>
         <v>0</v>
       </c>
       <c r="H43" s="6">
-        <f>IF(H$4="","",-H14/H16)</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="I43" s="6" t="e">
-        <f>IF(I$4="","",-I14/I16)</f>
+        <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
       <c r="J43" s="6" t="e">
-        <f>IF(J$4="","",-J14/J16)</f>
+        <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
       <c r="K43" s="6">
-        <f>IF(K$4="","",-K14/K16)</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="L43" s="6" t="e">
-        <f>IF(L$4="","",-L14/L16)</f>
+        <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
       <c r="M43" s="6">
-        <f>IF(M$4="","",-M14/M16)</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="N43" s="6">
-        <f>IF(N$4="","",-N14/N16)</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="O43" s="6" t="str">
-        <f>IF(O$4="","",-O14/O16)</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="P43" s="6" t="str">
-        <f>IF(P$4="","",-P14/P16)</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="Q43" s="6" t="str">
-        <f>IF(Q$4="","",-Q14/Q16)</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -7511,12 +7512,12 @@
     <row r="45" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A45" s="10"/>
       <c r="B45" s="59" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="C45" s="59"/>
       <c r="D45" s="61"/>
       <c r="E45" s="72" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F45" s="61"/>
       <c r="G45" s="38"/>
@@ -7534,13 +7535,13 @@
     <row r="46" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="10"/>
       <c r="B46" s="70" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="47" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="10"/>
       <c r="B47" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C47" s="229">
         <f>-BS!G31*Normalized_FCF!C53</f>
@@ -7594,7 +7595,7 @@
     <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C48" s="229">
         <f>BS!$C$65*C52</f>
@@ -7648,54 +7649,54 @@
     <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="10"/>
       <c r="B49" s="80" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C49" s="219">
         <f>C47+C48</f>
         <v>-589.42100000000005</v>
       </c>
       <c r="G49" s="219">
-        <f>IF(G4="","",G47+G48)</f>
+        <f t="shared" ref="G49:Q49" si="19">IF(G4="","",G47+G48)</f>
         <v>-521.5</v>
       </c>
       <c r="H49" s="219">
-        <f>IF(H4="","",H47+H48)</f>
+        <f t="shared" si="19"/>
         <v>-357.59999999999997</v>
       </c>
       <c r="I49" s="219">
-        <f>IF(I4="","",I47+I48)</f>
+        <f t="shared" si="19"/>
         <v>-337.7</v>
       </c>
       <c r="J49" s="219">
-        <f>IF(J4="","",J47+J48)</f>
+        <f t="shared" si="19"/>
         <v>-376</v>
       </c>
       <c r="K49" s="219">
-        <f>IF(K4="","",K47+K48)</f>
+        <f t="shared" si="19"/>
         <v>-559.6</v>
       </c>
       <c r="L49" s="219">
-        <f>IF(L4="","",L47+L48)</f>
+        <f t="shared" si="19"/>
         <v>-370.3</v>
       </c>
       <c r="M49" s="219">
-        <f>IF(M4="","",M47+M48)</f>
+        <f t="shared" si="19"/>
         <v>-243.7</v>
       </c>
       <c r="N49" s="219">
-        <f>IF(N4="","",N47+N48)</f>
+        <f t="shared" si="19"/>
         <v>-236.6</v>
       </c>
       <c r="O49" s="219" t="str">
-        <f>IF(O4="","",O47+O48)</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="P49" s="219" t="str">
-        <f>IF(P4="","",P47+P48)</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="Q49" s="219" t="str">
-        <f>IF(Q4="","",Q47+Q48)</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -7705,22 +7706,22 @@
     <row r="51" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="10"/>
       <c r="B51" s="82" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="G51" s="115" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
     </row>
     <row r="52" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="10"/>
       <c r="B52" s="8" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C52" s="100">
         <v>0.03</v>
       </c>
       <c r="E52" s="77" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G52" s="6">
         <f>IF(Normalized_FCF!G4="","",Normalized_FCF!G48/BS!$C$65)</f>
@@ -7740,14 +7741,14 @@
     <row r="53" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="10"/>
       <c r="B53" s="8" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C53" s="95">
         <f>Normalized_FCF!G53</f>
         <v>2.3771288224339427E-2</v>
       </c>
       <c r="E53" s="77" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G53" s="24">
         <f>IFERROR(ABS(Normalized_FCF!G47/BS!$G$31),0)</f>
@@ -7767,7 +7768,7 @@
     <row r="54" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="10"/>
       <c r="B54" s="27" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C54" s="44">
         <f>-C8/C47</f>
@@ -7778,43 +7779,43 @@
         <v>12.751632131705936</v>
       </c>
       <c r="H54" s="44">
-        <f t="shared" ref="H54:Q54" si="7">IF(H4="","",-H8/H47)</f>
+        <f t="shared" ref="H54:Q54" si="20">IF(H4="","",-H8/H47)</f>
         <v>12.770413392552097</v>
       </c>
       <c r="I54" s="44">
-        <f t="shared" si="7"/>
+        <f t="shared" si="20"/>
         <v>24.68433520876517</v>
       </c>
       <c r="J54" s="44">
-        <f t="shared" si="7"/>
+        <f t="shared" si="20"/>
         <v>21.772074468085123</v>
       </c>
       <c r="K54" s="44">
-        <f t="shared" si="7"/>
+        <f t="shared" si="20"/>
         <v>8.0407433881343877</v>
       </c>
       <c r="L54" s="44">
-        <f t="shared" si="7"/>
+        <f t="shared" si="20"/>
         <v>17.654604374831209</v>
       </c>
       <c r="M54" s="44">
-        <f t="shared" si="7"/>
+        <f t="shared" si="20"/>
         <v>21.556421830119003</v>
       </c>
       <c r="N54" s="44">
-        <f t="shared" si="7"/>
+        <f t="shared" si="20"/>
         <v>19.508030431107347</v>
       </c>
       <c r="O54" s="44" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="P54" s="44" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="Q54" s="44" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
@@ -7824,16 +7825,16 @@
     <row r="56" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="10"/>
       <c r="B56" s="70" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="G56" s="115" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
     </row>
     <row r="57" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="10"/>
       <c r="B57" s="42" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="C57" s="229">
         <f>BS!$C72*C65</f>
@@ -7887,7 +7888,7 @@
     <row r="58" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="10"/>
       <c r="B58" s="42" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="C58" s="229">
         <f>BS!$C67*C66</f>
@@ -7941,7 +7942,7 @@
     <row r="59" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="10"/>
       <c r="B59" s="42" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="C59" s="229">
         <f>BS!$C74*C67</f>
@@ -7995,67 +7996,67 @@
     <row r="60" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="10"/>
       <c r="B60" s="32" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="C60" s="219">
         <f>SUM(C57:C59)</f>
         <v>0</v>
       </c>
       <c r="G60" s="219">
-        <f>IF(G4="","",SUM(G57:G59))</f>
+        <f t="shared" ref="G60:Q60" si="21">IF(G4="","",SUM(G57:G59))</f>
         <v>0</v>
       </c>
       <c r="H60" s="219">
-        <f>IF(H4="","",SUM(H57:H59))</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="I60" s="219">
-        <f>IF(I4="","",SUM(I57:I59))</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="J60" s="219">
-        <f>IF(J4="","",SUM(J57:J59))</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="K60" s="219">
-        <f>IF(K4="","",SUM(K57:K59))</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="L60" s="219">
-        <f>IF(L4="","",SUM(L57:L59))</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="M60" s="219">
-        <f>IF(M4="","",SUM(M57:M59))</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="N60" s="219">
-        <f>IF(N4="","",SUM(N57:N59))</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="O60" s="219" t="str">
-        <f>IF(O4="","",SUM(O57:O59))</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="P60" s="219" t="str">
-        <f>IF(P4="","",SUM(P57:P59))</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="Q60" s="219" t="str">
-        <f>IF(Q4="","",SUM(Q57:Q59))</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
     <row r="61" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="10"/>
       <c r="B61" s="42" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="C61" s="236">
         <v>0</v>
       </c>
       <c r="E61" s="74" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="G61" s="229">
         <f>Data!C58</f>
@@ -8105,54 +8106,54 @@
     <row r="62" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="10"/>
       <c r="B62" s="32" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="C62" s="219">
         <f>C60+C61</f>
         <v>0</v>
       </c>
       <c r="G62" s="219">
-        <f>IF(G4="","",G60+G61)</f>
+        <f t="shared" ref="G62:Q62" si="22">IF(G4="","",G60+G61)</f>
         <v>-8463.2999999999993</v>
       </c>
       <c r="H62" s="219">
-        <f>IF(H4="","",H60+H61)</f>
+        <f t="shared" si="22"/>
         <v>-7013.1000000000013</v>
       </c>
       <c r="I62" s="219">
-        <f>IF(I4="","",I60+I61)</f>
+        <f t="shared" si="22"/>
         <v>-7830.5999999999976</v>
       </c>
       <c r="J62" s="219">
-        <f>IF(J4="","",J60+J61)</f>
+        <f t="shared" si="22"/>
         <v>-7660.6000000000067</v>
       </c>
       <c r="K62" s="219">
-        <f>IF(K4="","",K60+K61)</f>
+        <f t="shared" si="22"/>
         <v>-3857.9000000000042</v>
       </c>
       <c r="L62" s="219">
-        <f>IF(L4="","",L60+L61)</f>
+        <f t="shared" si="22"/>
         <v>-6059.9999999999964</v>
       </c>
       <c r="M62" s="219">
-        <f>IF(M4="","",M60+M61)</f>
+        <f t="shared" si="22"/>
         <v>-4901.2000000000007</v>
       </c>
       <c r="N62" s="219">
-        <f>IF(N4="","",N60+N61)</f>
+        <f t="shared" si="22"/>
         <v>-4283.1999999999989</v>
       </c>
       <c r="O62" s="219" t="str">
-        <f>IF(O4="","",O60+O61)</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="P62" s="219" t="str">
-        <f>IF(P4="","",P60+P61)</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="Q62" s="219" t="str">
-        <f>IF(Q4="","",Q60+Q61)</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
@@ -8162,16 +8163,16 @@
     <row r="64" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="10"/>
       <c r="B64" s="114" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="G64" s="115" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
     </row>
     <row r="65" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="10"/>
       <c r="B65" s="42" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="C65" s="212">
         <f>G65</f>
@@ -8195,7 +8196,7 @@
     <row r="66" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="10"/>
       <c r="B66" s="125" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="C66" s="212">
         <f>G66</f>
@@ -8219,7 +8220,7 @@
     <row r="67" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="10"/>
       <c r="B67" s="125" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="C67" s="212">
         <f>G67</f>
@@ -8243,7 +8244,7 @@
     <row r="68" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="10"/>
       <c r="B68" s="32" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="C68" s="81">
         <f>C60/BS!C69</f>
@@ -8273,12 +8274,12 @@
     <row r="70" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A70" s="10"/>
       <c r="B70" s="59" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="C70" s="59"/>
       <c r="D70" s="61"/>
       <c r="E70" s="72" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F70" s="61"/>
       <c r="G70" s="38"/>
@@ -8296,7 +8297,7 @@
     <row r="71" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A71" s="10"/>
       <c r="B71" s="82" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="C71" s="68"/>
       <c r="D71" s="28"/>
@@ -8317,7 +8318,7 @@
     <row r="72" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A72" s="10"/>
       <c r="B72" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C72" s="88">
         <f>ABS(C5/C$4)</f>
@@ -8327,54 +8328,54 @@
       <c r="E72" s="77"/>
       <c r="F72" s="28"/>
       <c r="G72" s="6">
-        <f>IF(G$4="","",ABS(G5/G$4))</f>
+        <f t="shared" ref="G72:Q72" si="23">IF(G$4="","",ABS(G5/G$4))</f>
         <v>0.8825181900968605</v>
       </c>
       <c r="H72" s="6">
-        <f>IF(H$4="","",ABS(H5/H$4))</f>
+        <f t="shared" si="23"/>
         <v>0.88174187088897438</v>
       </c>
       <c r="I72" s="6">
-        <f>IF(I$4="","",ABS(I5/I$4))</f>
+        <f t="shared" si="23"/>
         <v>0.77420437305496292</v>
       </c>
       <c r="J72" s="6">
-        <f>IF(J$4="","",ABS(J5/J$4))</f>
+        <f t="shared" si="23"/>
         <v>0.71388807333696291</v>
       </c>
       <c r="K72" s="6">
-        <f>IF(K$4="","",ABS(K5/K$4))</f>
+        <f t="shared" si="23"/>
         <v>0.71637051812485453</v>
       </c>
       <c r="L72" s="6">
-        <f>IF(L$4="","",ABS(L5/L$4))</f>
+        <f t="shared" si="23"/>
         <v>0.72094886207656972</v>
       </c>
       <c r="M72" s="6">
-        <f>IF(M$4="","",ABS(M5/M$4))</f>
+        <f t="shared" si="23"/>
         <v>0.72592314610084452</v>
       </c>
       <c r="N72" s="6">
-        <f>IF(N$4="","",ABS(N5/N$4))</f>
+        <f t="shared" si="23"/>
         <v>0.70801924071381883</v>
       </c>
       <c r="O72" s="6" t="str">
-        <f>IF(O$4="","",ABS(O5/O$4))</f>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="P72" s="6" t="str">
-        <f>IF(P$4="","",ABS(P5/P$4))</f>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="Q72" s="6" t="str">
-        <f>IF(Q$4="","",ABS(Q5/Q$4))</f>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
     <row r="73" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A73" s="10"/>
       <c r="B73" s="32" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C73" s="89">
         <f>ABS(C6/C$4)</f>
@@ -8384,54 +8385,54 @@
       <c r="E73" s="77"/>
       <c r="F73" s="28"/>
       <c r="G73" s="71">
-        <f>IF(G$4="","",ABS(G6/G$4))</f>
+        <f t="shared" ref="G73:Q73" si="24">IF(G$4="","",ABS(G6/G$4))</f>
         <v>0.11748180990313949</v>
       </c>
       <c r="H73" s="71">
-        <f>IF(H$4="","",ABS(H6/H$4))</f>
+        <f t="shared" si="24"/>
         <v>0.11825812911102566</v>
       </c>
       <c r="I73" s="71">
-        <f>IF(I$4="","",ABS(I6/I$4))</f>
+        <f t="shared" si="24"/>
         <v>0.2257956269450371</v>
       </c>
       <c r="J73" s="71">
-        <f>IF(J$4="","",ABS(J6/J$4))</f>
+        <f t="shared" si="24"/>
         <v>0.28611192666303714</v>
       </c>
       <c r="K73" s="71">
-        <f>IF(K$4="","",ABS(K6/K$4))</f>
+        <f t="shared" si="24"/>
         <v>0.28362948187514542</v>
       </c>
       <c r="L73" s="71">
-        <f>IF(L$4="","",ABS(L6/L$4))</f>
+        <f t="shared" si="24"/>
         <v>0.27905113792343034</v>
       </c>
       <c r="M73" s="71">
-        <f>IF(M$4="","",ABS(M6/M$4))</f>
+        <f t="shared" si="24"/>
         <v>0.27407685389915548</v>
       </c>
       <c r="N73" s="71">
-        <f>IF(N$4="","",ABS(N6/N$4))</f>
+        <f t="shared" si="24"/>
         <v>0.29198075928618117</v>
       </c>
       <c r="O73" s="71" t="str">
-        <f>IF(O$4="","",ABS(O6/O$4))</f>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="P73" s="71" t="str">
-        <f>IF(P$4="","",ABS(P6/P$4))</f>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="Q73" s="71" t="str">
-        <f>IF(Q$4="","",ABS(Q6/Q$4))</f>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="74" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A74" s="10"/>
       <c r="B74" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C74" s="88">
         <f>ABS(C7/C$4)</f>
@@ -8441,54 +8442,54 @@
       <c r="E74" s="77"/>
       <c r="F74" s="28"/>
       <c r="G74" s="6">
-        <f>IF(G$4="","",ABS(G7/G$4))</f>
+        <f t="shared" ref="G74:Q74" si="25">IF(G$4="","",ABS(G7/G$4))</f>
         <v>3.4834840359478626E-2</v>
       </c>
       <c r="H74" s="6">
-        <f>IF(H$4="","",ABS(H7/H$4))</f>
+        <f t="shared" si="25"/>
         <v>3.9303200949681254E-2</v>
       </c>
       <c r="I74" s="6">
-        <f>IF(I$4="","",ABS(I7/I$4))</f>
+        <f t="shared" si="25"/>
         <v>0.14154159637832697</v>
       </c>
       <c r="J74" s="6">
-        <f>IF(J$4="","",ABS(J7/J$4))</f>
+        <f t="shared" si="25"/>
         <v>0.16943780125933883</v>
       </c>
       <c r="K74" s="6">
-        <f>IF(K$4="","",ABS(K7/K$4))</f>
+        <f t="shared" si="25"/>
         <v>0.20434249385030695</v>
       </c>
       <c r="L74" s="6">
-        <f>IF(L$4="","",ABS(L7/L$4))</f>
+        <f t="shared" si="25"/>
         <v>0.18098015478338877</v>
       </c>
       <c r="M74" s="6">
-        <f>IF(M$4="","",ABS(M7/M$4))</f>
+        <f t="shared" si="25"/>
         <v>0.18527327558810205</v>
       </c>
       <c r="N74" s="6">
-        <f>IF(N$4="","",ABS(N7/N$4))</f>
+        <f t="shared" si="25"/>
         <v>0.20191236303675442</v>
       </c>
       <c r="O74" s="6" t="str">
-        <f>IF(O$4="","",ABS(O7/O$4))</f>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="P74" s="6" t="str">
-        <f>IF(P$4="","",ABS(P7/P$4))</f>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="Q74" s="6" t="str">
-        <f>IF(Q$4="","",ABS(Q7/Q$4))</f>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
     <row r="75" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A75" s="10"/>
       <c r="B75" s="30" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="C75" s="89">
         <f>ABS(C8/C$4)</f>
@@ -8498,54 +8499,54 @@
       <c r="E75" s="77"/>
       <c r="F75" s="28"/>
       <c r="G75" s="71">
-        <f>IF(G$4="","",ABS(G8/G$4))</f>
+        <f t="shared" ref="G75:Q75" si="26">IF(G$4="","",ABS(G8/G$4))</f>
         <v>8.2646969543660853E-2</v>
       </c>
       <c r="H75" s="71">
-        <f>IF(H$4="","",ABS(H8/H$4))</f>
+        <f t="shared" si="26"/>
         <v>7.8954928161344404E-2</v>
       </c>
       <c r="I75" s="71">
-        <f>IF(I$4="","",ABS(I8/I$4))</f>
+        <f t="shared" si="26"/>
         <v>8.4254030566710145E-2</v>
       </c>
       <c r="J75" s="71">
-        <f>IF(J$4="","",ABS(J8/J$4))</f>
+        <f t="shared" si="26"/>
         <v>0.11667412540369829</v>
       </c>
       <c r="K75" s="71">
-        <f>IF(K$4="","",ABS(K8/K$4))</f>
+        <f t="shared" si="26"/>
         <v>7.9286988024838481E-2</v>
       </c>
       <c r="L75" s="71">
-        <f>IF(L$4="","",ABS(L8/L$4))</f>
+        <f t="shared" si="26"/>
         <v>9.8070983140041562E-2</v>
       </c>
       <c r="M75" s="71">
-        <f>IF(M$4="","",ABS(M8/M$4))</f>
+        <f t="shared" si="26"/>
         <v>8.8803578311053427E-2</v>
       </c>
       <c r="N75" s="71">
-        <f>IF(N$4="","",ABS(N8/N$4))</f>
+        <f t="shared" si="26"/>
         <v>9.0068396249426752E-2</v>
       </c>
       <c r="O75" s="71" t="str">
-        <f>IF(O$4="","",ABS(O8/O$4))</f>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="P75" s="71" t="str">
-        <f>IF(P$4="","",ABS(P8/P$4))</f>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="Q75" s="71" t="str">
-        <f>IF(Q$4="","",ABS(Q8/Q$4))</f>
+        <f t="shared" si="26"/>
         <v/>
       </c>
     </row>
     <row r="76" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A76" s="10"/>
       <c r="B76" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C76" s="88">
         <f>ABS(C9/C$4)</f>
@@ -8555,54 +8556,54 @@
       <c r="E76" s="77"/>
       <c r="F76" s="28"/>
       <c r="G76" s="6">
-        <f>IF(G$4="","",G9/G$4)</f>
+        <f t="shared" ref="G76:Q76" si="27">IF(G$4="","",G9/G$4)</f>
         <v>0</v>
       </c>
       <c r="H76" s="6">
-        <f>IF(H$4="","",H9/H$4)</f>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="I76" s="6">
-        <f>IF(I$4="","",I9/I$4)</f>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="J76" s="6">
-        <f>IF(J$4="","",J9/J$4)</f>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="K76" s="6">
-        <f>IF(K$4="","",K9/K$4)</f>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="L76" s="6">
-        <f>IF(L$4="","",L9/L$4)</f>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="M76" s="6">
-        <f>IF(M$4="","",M9/M$4)</f>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="N76" s="6">
-        <f>IF(N$4="","",N9/N$4)</f>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="O76" s="6" t="str">
-        <f>IF(O$4="","",O9/O$4)</f>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="P76" s="6" t="str">
-        <f>IF(P$4="","",P9/P$4)</f>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="Q76" s="6" t="str">
-        <f>IF(Q$4="","",Q9/Q$4)</f>
+        <f t="shared" si="27"/>
         <v/>
       </c>
     </row>
     <row r="77" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A77" s="10"/>
       <c r="B77" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C77" s="101">
         <f>MAX(AVERAGE(G77:J77),C76)</f>
@@ -8610,58 +8611,58 @@
       </c>
       <c r="D77" s="28"/>
       <c r="E77" s="74" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F77" s="28"/>
       <c r="G77" s="6">
-        <f>IF(G$4="","",-G10/G$4)</f>
+        <f t="shared" ref="G77:Q77" si="28">IF(G$4="","",-G10/G$4)</f>
         <v>0</v>
       </c>
       <c r="H77" s="6">
-        <f>IF(H$4="","",-H10/H$4)</f>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="I77" s="6">
-        <f>IF(I$4="","",-I10/I$4)</f>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="J77" s="6">
-        <f>IF(J$4="","",-J10/J$4)</f>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="K77" s="6">
-        <f>IF(K$4="","",-K10/K$4)</f>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="L77" s="6">
-        <f>IF(L$4="","",-L10/L$4)</f>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="M77" s="6">
-        <f>IF(M$4="","",-M10/M$4)</f>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="N77" s="6">
-        <f>IF(N$4="","",-N10/N$4)</f>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="O77" s="6" t="str">
-        <f>IF(O$4="","",-O10/O$4)</f>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="P77" s="6" t="str">
-        <f>IF(P$4="","",-P10/P$4)</f>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="Q77" s="6" t="str">
-        <f>IF(Q$4="","",-Q10/Q$4)</f>
+        <f t="shared" si="28"/>
         <v/>
       </c>
     </row>
     <row r="78" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A78" s="10"/>
       <c r="B78" s="32" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="C78" s="89">
         <f>ABS(C11/C$4)</f>
@@ -8671,54 +8672,54 @@
       <c r="E78" s="77"/>
       <c r="F78" s="28"/>
       <c r="G78" s="71">
-        <f>IF(G$4="","",G11/G$4)</f>
+        <f t="shared" ref="G78:Q78" si="29">IF(G$4="","",G11/G$4)</f>
         <v>-7.7849935150349991E-2</v>
       </c>
       <c r="H78" s="71">
-        <f>IF(H$4="","",H11/H$4)</f>
+        <f t="shared" si="29"/>
         <v>-7.4068167512282929E-2</v>
       </c>
       <c r="I78" s="71">
-        <f>IF(I$4="","",I11/I$4)</f>
+        <f t="shared" si="29"/>
         <v>-7.9146776203610936E-2</v>
       </c>
       <c r="J78" s="71">
-        <f>IF(J$4="","",J11/J$4)</f>
+        <f t="shared" si="29"/>
         <v>-0.10918165777794256</v>
       </c>
       <c r="K78" s="71">
-        <f>IF(K$4="","",K11/K$4)</f>
+        <f t="shared" si="29"/>
         <v>-6.7979658436533127E-2</v>
       </c>
       <c r="L78" s="71">
-        <f>IF(L$4="","",L11/L$4)</f>
+        <f t="shared" si="29"/>
         <v>-9.090786353019531E-2</v>
       </c>
       <c r="M78" s="71">
-        <f>IF(M$4="","",M11/M$4)</f>
+        <f t="shared" si="29"/>
         <v>-8.2851559594566276E-2</v>
       </c>
       <c r="N78" s="71">
-        <f>IF(N$4="","",N11/N$4)</f>
+        <f t="shared" si="29"/>
         <v>-8.3581973051292294E-2</v>
       </c>
       <c r="O78" s="71" t="str">
-        <f>IF(O$4="","",O11/O$4)</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="P78" s="71" t="str">
-        <f>IF(P$4="","",P11/P$4)</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="Q78" s="71" t="str">
-        <f>IF(Q$4="","",Q11/Q$4)</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
     <row r="79" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A79" s="10"/>
       <c r="B79" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C79" s="88">
         <f>ABS(C12/C$4)</f>
@@ -8728,1446 +8729,1670 @@
       <c r="E79" s="77"/>
       <c r="F79" s="28"/>
       <c r="G79" s="6">
-        <f>IF(G$4="","",ABS(G12/G$4))</f>
+        <f t="shared" ref="G79:Q79" si="30">IF(G$4="","",ABS(G12/G$4))</f>
         <v>4.7970343933108279E-3</v>
       </c>
       <c r="H79" s="6">
-        <f>IF(H$4="","",ABS(H12/H$4))</f>
+        <f t="shared" si="30"/>
         <v>3.7767573116585201E-3</v>
       </c>
       <c r="I79" s="6">
-        <f>IF(I$4="","",ABS(I12/I$4))</f>
+        <f t="shared" si="30"/>
         <v>3.4132590508976859E-3</v>
       </c>
       <c r="J79" s="6">
-        <f>IF(J$4="","",ABS(J12/J$4))</f>
+        <f t="shared" si="30"/>
         <v>5.3588887717027868E-3</v>
       </c>
       <c r="K79" s="6">
-        <f>IF(K$4="","",ABS(K12/K$4))</f>
+        <f t="shared" si="30"/>
         <v>9.8606539467285034E-3</v>
       </c>
       <c r="L79" s="6">
-        <f>IF(L$4="","",ABS(L12/L$4))</f>
+        <f t="shared" si="30"/>
         <v>5.5549805058137539E-3</v>
       </c>
       <c r="M79" s="6">
-        <f>IF(M$4="","",ABS(M12/M$4))</f>
+        <f t="shared" si="30"/>
         <v>4.1195880750011828E-3</v>
       </c>
       <c r="N79" s="6">
-        <f>IF(N$4="","",ABS(N12/N$4))</f>
+        <f t="shared" si="30"/>
         <v>4.616990760164307E-3</v>
       </c>
       <c r="O79" s="6" t="str">
-        <f>IF(O$4="","",ABS(O12/O$4))</f>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="P79" s="6" t="str">
-        <f>IF(P$4="","",ABS(P12/P$4))</f>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="Q79" s="6" t="str">
-        <f>IF(Q$4="","",ABS(Q12/Q$4))</f>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
     <row r="80" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A80" s="10"/>
-      <c r="B80" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="C80" s="88">
-        <f>ABS(C14/C$4)</f>
-        <v>1.7196925478126027E-2</v>
+      <c r="B80" s="80" t="s">
+        <v>277</v>
+      </c>
+      <c r="C80" s="89">
+        <f>C13/C4</f>
+        <v>7.4769241209243581E-2</v>
       </c>
       <c r="D80" s="28"/>
       <c r="E80" s="77"/>
       <c r="F80" s="28"/>
-      <c r="G80" s="6">
-        <f>IF(G$4="","",ABS(G14/G$4))</f>
-        <v>0</v>
-      </c>
-      <c r="H80" s="6">
-        <f>IF(H$4="","",ABS(H14/H$4))</f>
-        <v>0</v>
-      </c>
-      <c r="I80" s="6">
-        <f>IF(I$4="","",ABS(I14/I$4))</f>
-        <v>0</v>
-      </c>
-      <c r="J80" s="6">
-        <f>IF(J$4="","",ABS(J14/J$4))</f>
-        <v>0</v>
-      </c>
-      <c r="K80" s="6">
-        <f>IF(K$4="","",ABS(K14/K$4))</f>
-        <v>0</v>
-      </c>
-      <c r="L80" s="6">
-        <f>IF(L$4="","",ABS(L14/L$4))</f>
-        <v>0</v>
-      </c>
-      <c r="M80" s="6">
-        <f>IF(M$4="","",ABS(M14/M$4))</f>
-        <v>0</v>
-      </c>
-      <c r="N80" s="6">
-        <f>IF(N$4="","",ABS(N14/N$4))</f>
-        <v>0</v>
-      </c>
-      <c r="O80" s="6" t="str">
-        <f>IF(O$4="","",ABS(O14/O$4))</f>
-        <v/>
-      </c>
-      <c r="P80" s="6" t="str">
-        <f>IF(P$4="","",ABS(P14/P$4))</f>
-        <v/>
-      </c>
-      <c r="Q80" s="6" t="str">
-        <f>IF(Q$4="","",ABS(Q14/Q$4))</f>
+      <c r="G80" s="71">
+        <f>IF(G$4="","",G13/G$4)</f>
+        <v>3.3464064160603729E-17</v>
+      </c>
+      <c r="H80" s="71">
+        <f t="shared" ref="H80:Q80" si="31">IF(H$4="","",H13/H$4)</f>
+        <v>1.1100033374029537E-3</v>
+      </c>
+      <c r="I80" s="71">
+        <f t="shared" si="31"/>
+        <v>1.6939953122015188E-3</v>
+      </c>
+      <c r="J80" s="71">
+        <f t="shared" si="31"/>
+        <v>2.1335788540529422E-3</v>
+      </c>
+      <c r="K80" s="71">
+        <f t="shared" si="31"/>
+        <v>1.4466756415768551E-3</v>
+      </c>
+      <c r="L80" s="71">
+        <f t="shared" si="31"/>
+        <v>1.6081391040324987E-3</v>
+      </c>
+      <c r="M80" s="71">
+        <f t="shared" si="31"/>
+        <v>1.8324306414859656E-3</v>
+      </c>
+      <c r="N80" s="71">
+        <f t="shared" si="31"/>
+        <v>1.8694324379701563E-3</v>
+      </c>
+      <c r="O80" s="71" t="str">
+        <f t="shared" si="31"/>
+        <v/>
+      </c>
+      <c r="P80" s="71" t="str">
+        <f t="shared" si="31"/>
+        <v/>
+      </c>
+      <c r="Q80" s="71" t="str">
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
     <row r="81" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A81" s="10"/>
-      <c r="B81" s="42" t="s">
-        <v>59</v>
-      </c>
-      <c r="C81" s="101">
-        <f>MIN(BS!D47,MAX(G81:K81))</f>
-        <v>2.1335788540529444E-3</v>
+      <c r="B81" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C81" s="88">
+        <f>ABS(C14/C$4)</f>
+        <v>1.7196925478126027E-2</v>
       </c>
       <c r="D81" s="28"/>
       <c r="E81" s="77"/>
       <c r="F81" s="28"/>
       <c r="G81" s="6">
-        <f>IF(G$4="","",-G15/G$4)</f>
-        <v>9.9252159355366879E-4</v>
+        <f t="shared" ref="G81:Q81" si="32">IF(G$4="","",ABS(G14/G$4))</f>
+        <v>0</v>
       </c>
       <c r="H81" s="6">
-        <f>IF(H$4="","",-H15/H$4)</f>
-        <v>1.1100033374029936E-3</v>
+        <f t="shared" si="32"/>
+        <v>0</v>
       </c>
       <c r="I81" s="6">
-        <f>IF(I$4="","",-I15/I$4)</f>
-        <v>1.6939953122015166E-3</v>
+        <f t="shared" si="32"/>
+        <v>0</v>
       </c>
       <c r="J81" s="6">
-        <f>IF(J$4="","",-J15/J$4)</f>
-        <v>2.1335788540529444E-3</v>
+        <f t="shared" si="32"/>
+        <v>0</v>
       </c>
       <c r="K81" s="6">
-        <f>IF(K$4="","",-K15/K$4)</f>
-        <v>1.4466756415768586E-3</v>
+        <f t="shared" si="32"/>
+        <v>0</v>
       </c>
       <c r="L81" s="6">
-        <f>IF(L$4="","",-L15/L$4)</f>
-        <v>1.6081391040324989E-3</v>
+        <f t="shared" si="32"/>
+        <v>0</v>
       </c>
       <c r="M81" s="6">
-        <f>IF(M$4="","",-M15/M$4)</f>
-        <v>1.8324306414859593E-3</v>
+        <f t="shared" si="32"/>
+        <v>0</v>
       </c>
       <c r="N81" s="6">
-        <f>IF(N$4="","",-N15/N$4)</f>
-        <v>1.8694324379701633E-3</v>
+        <f t="shared" si="32"/>
+        <v>0</v>
       </c>
       <c r="O81" s="6" t="str">
-        <f>IF(O$4="","",-O15/O$4)</f>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="P81" s="6" t="str">
-        <f>IF(P$4="","",-P15/P$4)</f>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="Q81" s="6" t="str">
-        <f>IF(Q$4="","",-Q15/Q$4)</f>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
     <row r="82" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A82" s="10"/>
-      <c r="B82" s="43" t="s">
-        <v>270</v>
-      </c>
-      <c r="C82" s="89">
-        <f>ABS(C16/C$4)</f>
-        <v>5.5438736877064618E-2</v>
+      <c r="B82" s="42" t="s">
+        <v>58</v>
+      </c>
+      <c r="C82" s="101">
+        <f>MIN(BS!D47,MAX(G82:K82))</f>
+        <v>2.1335788540529444E-3</v>
       </c>
       <c r="D82" s="28"/>
       <c r="E82" s="77"/>
       <c r="F82" s="28"/>
-      <c r="G82" s="71">
-        <f>IF(G$4="","",ABS(G16/G$4))</f>
-        <v>9.9252159355363539E-4</v>
-      </c>
-      <c r="H82" s="71">
-        <f>IF(H$4="","",ABS(H16/H$4))</f>
-        <v>3.992302168301994E-17</v>
-      </c>
-      <c r="I82" s="71">
-        <f>IF(I$4="","",ABS(I16/I$4))</f>
-        <v>0</v>
-      </c>
-      <c r="J82" s="71">
-        <f>IF(J$4="","",ABS(J16/J$4))</f>
-        <v>0</v>
-      </c>
-      <c r="K82" s="71">
-        <f>IF(K$4="","",ABS(K16/K$4))</f>
-        <v>3.5057120959145607E-18</v>
-      </c>
-      <c r="L82" s="71">
-        <f>IF(L$4="","",ABS(L16/L$4))</f>
-        <v>0</v>
-      </c>
-      <c r="M82" s="71">
-        <f>IF(M$4="","",ABS(M16/M$4))</f>
-        <v>6.2458537469361234E-18</v>
-      </c>
-      <c r="N82" s="71">
-        <f>IF(N$4="","",ABS(N16/N$4))</f>
-        <v>6.9327329790918243E-18</v>
-      </c>
-      <c r="O82" s="71" t="str">
-        <f>IF(O$4="","",ABS(O16/O$4))</f>
-        <v/>
-      </c>
-      <c r="P82" s="71" t="str">
-        <f>IF(P$4="","",ABS(P16/P$4))</f>
-        <v/>
-      </c>
-      <c r="Q82" s="71" t="str">
-        <f>IF(Q$4="","",ABS(Q16/Q$4))</f>
+      <c r="G82" s="6">
+        <f t="shared" ref="G82:Q82" si="33">IF(G$4="","",-G15/G$4)</f>
+        <v>9.9252159355366879E-4</v>
+      </c>
+      <c r="H82" s="6">
+        <f t="shared" si="33"/>
+        <v>1.1100033374029936E-3</v>
+      </c>
+      <c r="I82" s="6">
+        <f t="shared" si="33"/>
+        <v>1.6939953122015166E-3</v>
+      </c>
+      <c r="J82" s="6">
+        <f t="shared" si="33"/>
+        <v>2.1335788540529444E-3</v>
+      </c>
+      <c r="K82" s="6">
+        <f t="shared" si="33"/>
+        <v>1.4466756415768586E-3</v>
+      </c>
+      <c r="L82" s="6">
+        <f t="shared" si="33"/>
+        <v>1.6081391040324989E-3</v>
+      </c>
+      <c r="M82" s="6">
+        <f t="shared" si="33"/>
+        <v>1.8324306414859593E-3</v>
+      </c>
+      <c r="N82" s="6">
+        <f t="shared" si="33"/>
+        <v>1.8694324379701633E-3</v>
+      </c>
+      <c r="O82" s="6" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="P82" s="6" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="Q82" s="6" t="str">
+        <f t="shared" si="33"/>
         <v/>
       </c>
     </row>
     <row r="83" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A83" s="10"/>
-      <c r="B83" s="28" t="s">
-        <v>69</v>
-      </c>
-      <c r="C83" s="101">
-        <f>MIN(AVERAGE(G83:J83)/2,0)</f>
-        <v>0</v>
+      <c r="B83" s="43" t="s">
+        <v>266</v>
+      </c>
+      <c r="C83" s="89">
+        <f>ABS(C16/C$4)</f>
+        <v>5.5438736877064618E-2</v>
       </c>
       <c r="D83" s="28"/>
-      <c r="E83" s="76" t="str">
+      <c r="E83" s="77"/>
+      <c r="F83" s="28"/>
+      <c r="G83" s="71">
+        <f t="shared" ref="G83:Q83" si="34">IF(G$4="","",ABS(G16/G$4))</f>
+        <v>9.9252159355363539E-4</v>
+      </c>
+      <c r="H83" s="71">
+        <f t="shared" si="34"/>
+        <v>3.992302168301994E-17</v>
+      </c>
+      <c r="I83" s="71">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="J83" s="71">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="K83" s="71">
+        <f t="shared" si="34"/>
+        <v>3.5057120959145607E-18</v>
+      </c>
+      <c r="L83" s="71">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="M83" s="71">
+        <f t="shared" si="34"/>
+        <v>6.2458537469361234E-18</v>
+      </c>
+      <c r="N83" s="71">
+        <f t="shared" si="34"/>
+        <v>6.9327329790918243E-18</v>
+      </c>
+      <c r="O83" s="71" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="P83" s="71" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="Q83" s="71" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+    </row>
+    <row r="84" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A84" s="10"/>
+      <c r="B84" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="C84" s="101">
+        <f>MIN(AVERAGE(G84:J84)/2,0)</f>
+        <v>0</v>
+      </c>
+      <c r="D84" s="28"/>
+      <c r="E84" s="76" t="str">
         <f>E17</f>
         <v>WCInv is excluded</v>
       </c>
-      <c r="F83" s="28"/>
-      <c r="G83" s="6">
-        <f>IF(G$4="","",-G17/G$4)</f>
-        <v>0</v>
-      </c>
-      <c r="H83" s="6">
-        <f>IF(H$4="","",-H17/H$4)</f>
-        <v>0</v>
-      </c>
-      <c r="I83" s="6">
-        <f>IF(I$4="","",-I17/I$4)</f>
-        <v>0</v>
-      </c>
-      <c r="J83" s="6">
-        <f>IF(J$4="","",-J17/J$4)</f>
-        <v>0</v>
-      </c>
-      <c r="K83" s="6">
-        <f>IF(K$4="","",-K17/K$4)</f>
-        <v>0</v>
-      </c>
-      <c r="L83" s="6">
-        <f>IF(L$4="","",-L17/L$4)</f>
-        <v>0</v>
-      </c>
-      <c r="M83" s="6">
-        <f>IF(M$4="","",-M17/M$4)</f>
-        <v>0</v>
-      </c>
-      <c r="N83" s="6">
-        <f>IF(N$4="","",-N17/N$4)</f>
-        <v>0</v>
-      </c>
-      <c r="O83" s="6" t="str">
-        <f>IF(O$4="","",-O17/O$4)</f>
-        <v/>
-      </c>
-      <c r="P83" s="6" t="str">
-        <f>IF(P$4="","",-P17/P$4)</f>
-        <v/>
-      </c>
-      <c r="Q83" s="6" t="str">
-        <f>IF(Q$4="","",-Q17/Q$4)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="84" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="10"/>
-      <c r="B84" s="8" t="s">
-        <v>176</v>
-      </c>
-      <c r="C84" s="101">
-        <v>0</v>
-      </c>
-      <c r="E84" s="76" t="str">
+      <c r="F84" s="28"/>
+      <c r="G84" s="6">
+        <f t="shared" ref="G84:Q84" si="35">IF(G$4="","",-G17/G$4)</f>
+        <v>0</v>
+      </c>
+      <c r="H84" s="6">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="I84" s="6">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="J84" s="6">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="K84" s="6">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="L84" s="6">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="M84" s="6">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="N84" s="6">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="O84" s="6" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+      <c r="P84" s="6" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+      <c r="Q84" s="6" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+    </row>
+    <row r="85" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A85" s="10"/>
+      <c r="B85" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="C85" s="101">
+        <v>0</v>
+      </c>
+      <c r="E85" s="76" t="str">
         <f>E18</f>
         <v>Net borrowing is excluded</v>
       </c>
-      <c r="G84" s="202"/>
-      <c r="H84" s="202"/>
-      <c r="I84" s="202"/>
-      <c r="J84" s="202"/>
-      <c r="K84" s="202"/>
-      <c r="L84" s="202"/>
-      <c r="M84" s="202"/>
-      <c r="N84" s="202"/>
-      <c r="O84" s="202"/>
-      <c r="P84" s="202"/>
-      <c r="Q84" s="202"/>
-    </row>
-    <row r="85" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="10"/>
-      <c r="B85" s="32" t="s">
-        <v>242</v>
-      </c>
-      <c r="C85" s="89">
+      <c r="G85" s="202"/>
+      <c r="H85" s="202"/>
+      <c r="I85" s="202"/>
+      <c r="J85" s="202"/>
+      <c r="K85" s="202"/>
+      <c r="L85" s="202"/>
+      <c r="M85" s="202"/>
+      <c r="N85" s="202"/>
+      <c r="O85" s="202"/>
+      <c r="P85" s="202"/>
+      <c r="Q85" s="202"/>
+    </row>
+    <row r="86" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A86" s="10"/>
+      <c r="B86" s="32" t="s">
+        <v>238</v>
+      </c>
+      <c r="C86" s="89">
         <f>ABS(C19/C$4)</f>
         <v>5.5438736877064618E-2</v>
       </c>
-      <c r="D85" s="86"/>
-      <c r="E85" s="77"/>
-      <c r="F85" s="86"/>
-      <c r="G85" s="71">
-        <f>IF(G$4="","",ABS(G19/G$4))</f>
+      <c r="D86" s="86"/>
+      <c r="E86" s="77"/>
+      <c r="F86" s="86"/>
+      <c r="G86" s="71">
+        <f t="shared" ref="G86:Q86" si="36">IF(G$4="","",ABS(G19/G$4))</f>
         <v>9.9252159355363539E-4</v>
       </c>
-      <c r="H85" s="71">
-        <f>IF(H$4="","",ABS(H19/H$4))</f>
+      <c r="H86" s="71">
+        <f t="shared" si="36"/>
         <v>3.992302168301994E-17</v>
       </c>
-      <c r="I85" s="71">
-        <f>IF(I$4="","",ABS(I19/I$4))</f>
-        <v>0</v>
-      </c>
-      <c r="J85" s="71">
-        <f>IF(J$4="","",ABS(J19/J$4))</f>
-        <v>0</v>
-      </c>
-      <c r="K85" s="71">
-        <f>IF(K$4="","",ABS(K19/K$4))</f>
+      <c r="I86" s="71">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="J86" s="71">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="K86" s="71">
+        <f t="shared" si="36"/>
         <v>3.5057120959145607E-18</v>
       </c>
-      <c r="L85" s="71">
-        <f>IF(L$4="","",ABS(L19/L$4))</f>
-        <v>0</v>
-      </c>
-      <c r="M85" s="71">
-        <f>IF(M$4="","",ABS(M19/M$4))</f>
+      <c r="L86" s="71">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="M86" s="71">
+        <f t="shared" si="36"/>
         <v>6.2458537469361234E-18</v>
       </c>
-      <c r="N85" s="71">
-        <f>IF(N$4="","",ABS(N19/N$4))</f>
+      <c r="N86" s="71">
+        <f t="shared" si="36"/>
         <v>6.9327329790918243E-18</v>
       </c>
-      <c r="O85" s="71" t="str">
-        <f>IF(O$4="","",ABS(O19/O$4))</f>
-        <v/>
-      </c>
-      <c r="P85" s="71" t="str">
-        <f>IF(P$4="","",ABS(P19/P$4))</f>
-        <v/>
-      </c>
-      <c r="Q85" s="71" t="str">
-        <f>IF(Q$4="","",ABS(Q19/Q$4))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="86" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="10"/>
+      <c r="O86" s="71" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="P86" s="71" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="Q86" s="71" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
     </row>
     <row r="87" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A87" s="10"/>
-      <c r="B87" s="105" t="s">
-        <v>348</v>
-      </c>
-      <c r="C87" s="27"/>
-      <c r="D87" s="27"/>
-      <c r="E87" s="27"/>
-      <c r="F87" s="27"/>
-      <c r="G87" s="115" t="s">
-        <v>347</v>
-      </c>
-      <c r="H87" s="12"/>
-      <c r="I87" s="12"/>
-      <c r="J87" s="12"/>
-      <c r="K87" s="12"/>
-      <c r="L87" s="12"/>
-      <c r="M87" s="12"/>
-      <c r="N87" s="12"/>
-      <c r="O87" s="12"/>
-      <c r="P87" s="12"/>
-      <c r="Q87" s="12"/>
     </row>
     <row r="88" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A88" s="10"/>
-      <c r="B88" s="27" t="s">
-        <v>345</v>
-      </c>
-      <c r="C88" s="112">
-        <f>C103/C$4</f>
-        <v>5.8036265058208601E-2</v>
-      </c>
-      <c r="D88" s="27"/>
-      <c r="E88" s="27"/>
-      <c r="F88" s="27"/>
-      <c r="G88" s="112">
-        <f>IF(G$4="","",G103/G$4)</f>
-        <v>1.9668576895127539</v>
-      </c>
-      <c r="H88" s="112">
-        <f>IF(H$4="","",H103/H$4)</f>
-        <v>1.9824913079662543</v>
-      </c>
-      <c r="I88" s="112">
-        <f>IF(I$4="","",I103/I$4)</f>
-        <v>2.8031579468695957</v>
-      </c>
-      <c r="J88" s="112">
-        <f>IF(J$4="","",J103/J$4)</f>
-        <v>0</v>
-      </c>
-      <c r="K88" s="112">
-        <f>IF(K$4="","",K103/K$4)</f>
-        <v>0</v>
-      </c>
-      <c r="L88" s="112">
-        <f>IF(L$4="","",L103/L$4)</f>
-        <v>0</v>
-      </c>
-      <c r="M88" s="112">
-        <f>IF(M$4="","",M103/M$4)</f>
-        <v>0</v>
-      </c>
-      <c r="N88" s="112">
-        <f>IF(N$4="","",N103/N$4)</f>
-        <v>0</v>
-      </c>
-      <c r="O88" s="112" t="str">
-        <f>IF(O$4="","",O103/O$4)</f>
-        <v/>
-      </c>
-      <c r="P88" s="112" t="str">
-        <f>IF(P$4="","",P103/P$4)</f>
-        <v/>
-      </c>
-      <c r="Q88" s="112" t="str">
-        <f>IF(Q$4="","",Q103/Q$4)</f>
-        <v/>
+      <c r="B88" s="70" t="s">
+        <v>338</v>
       </c>
     </row>
     <row r="89" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A89" s="10"/>
-      <c r="B89" s="27" t="s">
-        <v>346</v>
-      </c>
-      <c r="C89" s="112">
-        <f>C104/C$4</f>
-        <v>0.67109640924920733</v>
-      </c>
-      <c r="D89" s="27"/>
-      <c r="E89" s="27"/>
-      <c r="F89" s="27"/>
-      <c r="G89" s="112">
-        <f>IF(G$4="","",G104/G$4)</f>
-        <v>81.431024808440569</v>
-      </c>
-      <c r="H89" s="112">
-        <f>IF(H$4="","",H104/H$4)</f>
-        <v>92.616143736455001</v>
-      </c>
-      <c r="I89" s="112">
-        <f>IF(I$4="","",I104/I$4)</f>
-        <v>74.002266072488041</v>
-      </c>
-      <c r="J89" s="112">
-        <f>IF(J$4="","",J104/J$4)</f>
-        <v>0</v>
-      </c>
-      <c r="K89" s="112">
-        <f>IF(K$4="","",K104/K$4)</f>
-        <v>0</v>
-      </c>
-      <c r="L89" s="112">
-        <f>IF(L$4="","",L104/L$4)</f>
-        <v>0</v>
-      </c>
-      <c r="M89" s="112">
-        <f>IF(M$4="","",M104/M$4)</f>
-        <v>0</v>
-      </c>
-      <c r="N89" s="112">
-        <f>IF(N$4="","",N104/N$4)</f>
-        <v>0</v>
-      </c>
-      <c r="O89" s="112" t="str">
-        <f>IF(O$4="","",O104/O$4)</f>
-        <v/>
-      </c>
-      <c r="P89" s="112" t="str">
-        <f>IF(P$4="","",P104/P$4)</f>
-        <v/>
-      </c>
-      <c r="Q89" s="112" t="str">
-        <f>IF(Q$4="","",Q104/Q$4)</f>
+      <c r="B89" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C89" s="136">
+        <f>G89</f>
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="G89" s="135">
+        <f>Data!C64</f>
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="H89" s="135">
+        <f>Data!D64</f>
+        <v>0</v>
+      </c>
+      <c r="I89" s="135">
+        <f>Data!E64</f>
+        <v>0</v>
+      </c>
+      <c r="J89" s="135">
+        <f>Data!F64</f>
+        <v>0</v>
+      </c>
+      <c r="K89" s="135">
+        <f>Data!G64</f>
+        <v>0</v>
+      </c>
+      <c r="L89" s="135">
+        <f>Data!H64</f>
+        <v>0</v>
+      </c>
+      <c r="M89" s="135">
+        <f>Data!I64</f>
+        <v>0</v>
+      </c>
+      <c r="N89" s="135">
+        <f>Data!J64</f>
+        <v>0</v>
+      </c>
+      <c r="O89" s="135" t="str">
+        <f>Data!K64</f>
+        <v/>
+      </c>
+      <c r="P89" s="135" t="str">
+        <f>Data!L64</f>
+        <v/>
+      </c>
+      <c r="Q89" s="135" t="str">
+        <f>Data!M64</f>
         <v/>
       </c>
     </row>
     <row r="90" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A90" s="10"/>
-      <c r="B90" s="27" t="s">
-        <v>129</v>
-      </c>
-      <c r="C90" s="112">
-        <f>BS!$G$38/C$4</f>
-        <v>0</v>
-      </c>
-      <c r="D90" s="27"/>
-      <c r="E90" s="27"/>
-      <c r="F90" s="27"/>
-      <c r="G90" s="112">
-        <f>BS!$G$38/G$4</f>
-        <v>0</v>
-      </c>
-      <c r="H90" s="266"/>
-      <c r="I90" s="266"/>
-      <c r="J90" s="266"/>
-      <c r="K90" s="266"/>
-      <c r="L90" s="266"/>
-      <c r="M90" s="266"/>
-      <c r="N90" s="266"/>
-      <c r="O90" s="266"/>
-      <c r="P90" s="266"/>
-      <c r="Q90" s="266"/>
+      <c r="B90" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C90" s="85">
+        <f>C89*Common_Shares/$C$3</f>
+        <v>5493.2552400000004</v>
+      </c>
+      <c r="G90" s="85">
+        <f t="shared" ref="G90:Q90" si="37">IF(G$4="","",G89*Common_Shares/$C$3)</f>
+        <v>5493.2552400000004</v>
+      </c>
+      <c r="H90" s="85">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="I90" s="85">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="J90" s="85">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="K90" s="85">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="L90" s="85">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="M90" s="85">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="N90" s="85">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="O90" s="85" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="P90" s="85" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="Q90" s="85" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
     </row>
     <row r="91" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A91" s="10"/>
+      <c r="B91" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="C91" s="24">
+        <f>C89/(C19*$C$3/Common_Shares)</f>
+        <v>0.98321645122101553</v>
+      </c>
+      <c r="G91" s="203">
+        <f t="shared" ref="G91:Q91" si="38">IF(G$4="","",G89/(G19*$C$3/Common_Shares))</f>
+        <v>-50.910613901762609</v>
+      </c>
+      <c r="H91" s="203">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="I91" s="203" t="e">
+        <f t="shared" si="38"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J91" s="203" t="e">
+        <f t="shared" si="38"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K91" s="203">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="L91" s="203" t="e">
+        <f t="shared" si="38"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M91" s="203">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="N91" s="203">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="O91" s="203" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="P91" s="203" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="Q91" s="203" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
     </row>
     <row r="92" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A92" s="10"/>
-      <c r="B92" s="70" t="s">
-        <v>342</v>
-      </c>
     </row>
     <row r="93" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="10"/>
-      <c r="B93" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C93" s="136">
-        <f>G93</f>
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="G93" s="135">
-        <f>Data!C64</f>
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="H93" s="135">
-        <f>Data!D64</f>
-        <v>0</v>
-      </c>
-      <c r="I93" s="135">
-        <f>Data!E64</f>
-        <v>0</v>
-      </c>
-      <c r="J93" s="135">
-        <f>Data!F64</f>
-        <v>0</v>
-      </c>
-      <c r="K93" s="135">
-        <f>Data!G64</f>
-        <v>0</v>
-      </c>
-      <c r="L93" s="135">
-        <f>Data!H64</f>
-        <v>0</v>
-      </c>
-      <c r="M93" s="135">
-        <f>Data!I64</f>
-        <v>0</v>
-      </c>
-      <c r="N93" s="135">
-        <f>Data!J64</f>
-        <v>0</v>
-      </c>
-      <c r="O93" s="135" t="str">
-        <f>Data!K64</f>
-        <v/>
-      </c>
-      <c r="P93" s="135" t="str">
-        <f>Data!L64</f>
-        <v/>
-      </c>
-      <c r="Q93" s="135" t="str">
-        <f>Data!M64</f>
-        <v/>
-      </c>
+      <c r="B93" s="184" t="s">
+        <v>152</v>
+      </c>
+      <c r="C93" s="68"/>
+      <c r="D93" s="28"/>
+      <c r="E93" s="77"/>
+      <c r="F93" s="28"/>
+      <c r="G93" s="12"/>
+      <c r="H93" s="12"/>
+      <c r="I93" s="12"/>
+      <c r="J93" s="12"/>
+      <c r="K93" s="12"/>
+      <c r="L93" s="12"/>
+      <c r="M93" s="12"/>
+      <c r="N93" s="12"/>
+      <c r="O93" s="12"/>
+      <c r="P93" s="12"/>
+      <c r="Q93" s="12"/>
     </row>
     <row r="94" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A94" s="10"/>
-      <c r="B94" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="C94" s="85">
-        <f>C93*Common_Shares/$C$3</f>
-        <v>5493.2552400000004</v>
-      </c>
-      <c r="G94" s="85">
-        <f>IF(G$4="","",G93*Common_Shares/$C$3)</f>
-        <v>5493.2552400000004</v>
-      </c>
-      <c r="H94" s="85">
-        <f>IF(H$4="","",H93*Common_Shares/$C$3)</f>
-        <v>0</v>
-      </c>
-      <c r="I94" s="85">
-        <f>IF(I$4="","",I93*Common_Shares/$C$3)</f>
-        <v>0</v>
-      </c>
-      <c r="J94" s="85">
-        <f>IF(J$4="","",J93*Common_Shares/$C$3)</f>
-        <v>0</v>
-      </c>
-      <c r="K94" s="85">
-        <f>IF(K$4="","",K93*Common_Shares/$C$3)</f>
-        <v>0</v>
-      </c>
-      <c r="L94" s="85">
-        <f>IF(L$4="","",L93*Common_Shares/$C$3)</f>
-        <v>0</v>
-      </c>
-      <c r="M94" s="85">
-        <f>IF(M$4="","",M93*Common_Shares/$C$3)</f>
-        <v>0</v>
-      </c>
-      <c r="N94" s="85">
-        <f>IF(N$4="","",N93*Common_Shares/$C$3)</f>
-        <v>0</v>
-      </c>
-      <c r="O94" s="85" t="str">
-        <f>IF(O$4="","",O93*Common_Shares/$C$3)</f>
-        <v/>
-      </c>
-      <c r="P94" s="85" t="str">
-        <f>IF(P$4="","",P93*Common_Shares/$C$3)</f>
-        <v/>
-      </c>
-      <c r="Q94" s="85" t="str">
-        <f>IF(Q$4="","",Q93*Common_Shares/$C$3)</f>
+      <c r="B94" s="28" t="s">
+        <v>242</v>
+      </c>
+      <c r="C94" s="88">
+        <f>C4/G4-1</f>
+        <v>-7.2986977944986764E-2</v>
+      </c>
+      <c r="D94" s="28"/>
+      <c r="E94" s="77"/>
+      <c r="F94" s="28"/>
+      <c r="G94" s="6">
+        <f t="shared" ref="G94:Q94" si="39">IF(H4="","",G4/H4-1)</f>
+        <v>0.14816168238907368</v>
+      </c>
+      <c r="H94" s="6">
+        <f t="shared" si="39"/>
+        <v>-4.2989679363882538E-2</v>
+      </c>
+      <c r="I94" s="6">
+        <f t="shared" si="39"/>
+        <v>0.41009608943643294</v>
+      </c>
+      <c r="J94" s="6">
+        <f t="shared" si="39"/>
+        <v>0.23634909111413416</v>
+      </c>
+      <c r="K94" s="6">
+        <f t="shared" si="39"/>
+        <v>-0.14866435946709378</v>
+      </c>
+      <c r="L94" s="6">
+        <f t="shared" si="39"/>
+        <v>0.12685863237113804</v>
+      </c>
+      <c r="M94" s="6">
+        <f t="shared" si="39"/>
+        <v>0.15437257905572199</v>
+      </c>
+      <c r="N94" s="6" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="O94" s="6" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="P94" s="6" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="Q94" s="6" t="str">
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
     <row r="95" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A95" s="10"/>
-      <c r="B95" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="C95" s="24">
-        <f>C93/(C19*$C$3/Common_Shares)</f>
-        <v>0.98321645122101553</v>
-      </c>
-      <c r="G95" s="203">
-        <f>IF(G$4="","",G93/(G19*$C$3/Common_Shares))</f>
-        <v>-50.910613901762609</v>
-      </c>
-      <c r="H95" s="203">
-        <f>IF(H$4="","",H93/(H19*$C$3/Common_Shares))</f>
-        <v>0</v>
-      </c>
-      <c r="I95" s="203" t="e">
-        <f>IF(I$4="","",I93/(I19*$C$3/Common_Shares))</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J95" s="203" t="e">
-        <f>IF(J$4="","",J93/(J19*$C$3/Common_Shares))</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K95" s="203">
-        <f>IF(K$4="","",K93/(K19*$C$3/Common_Shares))</f>
-        <v>0</v>
-      </c>
-      <c r="L95" s="203" t="e">
-        <f>IF(L$4="","",L93/(L19*$C$3/Common_Shares))</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M95" s="203">
-        <f>IF(M$4="","",M93/(M19*$C$3/Common_Shares))</f>
-        <v>0</v>
-      </c>
-      <c r="N95" s="203">
-        <f>IF(N$4="","",N93/(N19*$C$3/Common_Shares))</f>
-        <v>0</v>
-      </c>
-      <c r="O95" s="203" t="str">
-        <f>IF(O$4="","",O93/(O19*$C$3/Common_Shares))</f>
-        <v/>
-      </c>
-      <c r="P95" s="203" t="str">
-        <f>IF(P$4="","",P93/(P19*$C$3/Common_Shares))</f>
-        <v/>
-      </c>
-      <c r="Q95" s="203" t="str">
-        <f>IF(Q$4="","",Q93/(Q19*$C$3/Common_Shares))</f>
+      <c r="B95" s="80" t="s">
+        <v>277</v>
+      </c>
+      <c r="C95" s="88">
+        <f>C13/G13-1</f>
+        <v>2071238565569694.8</v>
+      </c>
+      <c r="D95" s="28"/>
+      <c r="E95" s="77"/>
+      <c r="F95" s="28"/>
+      <c r="G95" s="6">
+        <f t="shared" ref="G95:Q95" si="40">IF(H5="","",G13/H13-1)</f>
+        <v>-0.99999999999996536</v>
+      </c>
+      <c r="H95" s="6">
+        <f t="shared" si="40"/>
+        <v>-0.37291169451076311</v>
+      </c>
+      <c r="I95" s="6">
+        <f t="shared" si="40"/>
+        <v>0.11957247828991591</v>
+      </c>
+      <c r="J95" s="6">
+        <f t="shared" si="40"/>
+        <v>0.82338611449452115</v>
+      </c>
+      <c r="K95" s="6">
+        <f t="shared" si="40"/>
+        <v>-0.23414179104477795</v>
+      </c>
+      <c r="L95" s="6">
+        <f t="shared" si="40"/>
+        <v>-1.1070110701110525E-2</v>
+      </c>
+      <c r="M95" s="6">
+        <f t="shared" si="40"/>
+        <v>0.13152400835073874</v>
+      </c>
+      <c r="N95" s="6" t="str">
+        <f t="shared" si="40"/>
+        <v/>
+      </c>
+      <c r="O95" s="6" t="str">
+        <f t="shared" si="40"/>
+        <v/>
+      </c>
+      <c r="P95" s="6" t="str">
+        <f t="shared" si="40"/>
+        <v/>
+      </c>
+      <c r="Q95" s="6" t="str">
+        <f t="shared" si="40"/>
         <v/>
       </c>
     </row>
     <row r="96" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A96" s="10"/>
     </row>
-    <row r="97" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="10"/>
-      <c r="B97" s="184" t="s">
-        <v>153</v>
-      </c>
-      <c r="C97" s="68"/>
-      <c r="D97" s="28"/>
-      <c r="E97" s="77"/>
-      <c r="F97" s="28"/>
-      <c r="G97" s="12"/>
-      <c r="H97" s="12"/>
-      <c r="I97" s="12"/>
-      <c r="J97" s="12"/>
-      <c r="K97" s="12"/>
-      <c r="L97" s="12"/>
-      <c r="M97" s="12"/>
-      <c r="N97" s="12"/>
-      <c r="O97" s="12"/>
-      <c r="P97" s="12"/>
-      <c r="Q97" s="12"/>
+    <row r="97" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A97" s="3"/>
+      <c r="B97" s="59" t="s">
+        <v>339</v>
+      </c>
+      <c r="C97" s="59"/>
+      <c r="D97" s="61"/>
+      <c r="E97" s="72" t="s">
+        <v>118</v>
+      </c>
+      <c r="F97" s="61"/>
+      <c r="G97" s="38"/>
+      <c r="H97" s="38"/>
+      <c r="I97" s="38"/>
+      <c r="J97" s="38"/>
+      <c r="K97" s="38"/>
+      <c r="L97" s="38"/>
+      <c r="M97" s="38"/>
+      <c r="N97" s="38"/>
+      <c r="O97" s="38"/>
+      <c r="P97" s="38"/>
+      <c r="Q97" s="38"/>
     </row>
     <row r="98" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A98" s="10"/>
-      <c r="B98" s="28" t="s">
-        <v>246</v>
-      </c>
-      <c r="C98" s="88">
-        <f>C4/G4-1</f>
-        <v>-7.2986977944986764E-2</v>
-      </c>
-      <c r="D98" s="28"/>
-      <c r="E98" s="77"/>
-      <c r="F98" s="28"/>
-      <c r="G98" s="6">
-        <f>IF(H4="","",G4/H4-1)</f>
-        <v>0.14816168238907368</v>
-      </c>
-      <c r="H98" s="6">
-        <f>IF(I4="","",H4/I4-1)</f>
-        <v>-4.2989679363882538E-2</v>
-      </c>
-      <c r="I98" s="6">
-        <f>IF(J4="","",I4/J4-1)</f>
-        <v>0.41009608943643294</v>
-      </c>
-      <c r="J98" s="6">
-        <f>IF(K4="","",J4/K4-1)</f>
-        <v>0.23634909111413416</v>
-      </c>
-      <c r="K98" s="6">
-        <f>IF(L4="","",K4/L4-1)</f>
-        <v>-0.14866435946709378</v>
-      </c>
-      <c r="L98" s="6">
-        <f>IF(M4="","",L4/M4-1)</f>
-        <v>0.12685863237113804</v>
-      </c>
-      <c r="M98" s="6">
-        <f>IF(N4="","",M4/N4-1)</f>
-        <v>0.15437257905572199</v>
-      </c>
-      <c r="N98" s="6" t="str">
-        <f>IF(O4="","",N4/O4-1)</f>
-        <v/>
-      </c>
-      <c r="O98" s="6" t="str">
-        <f>IF(P4="","",O4/P4-1)</f>
-        <v/>
-      </c>
-      <c r="P98" s="6" t="str">
-        <f>IF(Q4="","",P4/Q4-1)</f>
-        <v/>
-      </c>
-      <c r="Q98" s="6" t="str">
-        <f>IF(R4="","",Q4/R4-1)</f>
-        <v/>
+      <c r="B98" s="70" t="s">
+        <v>31</v>
+      </c>
+      <c r="G98" s="115" t="s">
+        <v>343</v>
       </c>
     </row>
     <row r="99" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A99" s="10"/>
-    </row>
-    <row r="100" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A100" s="3"/>
-      <c r="B100" s="59" t="s">
-        <v>343</v>
-      </c>
-      <c r="C100" s="59"/>
-      <c r="D100" s="61"/>
-      <c r="E100" s="72" t="s">
-        <v>119</v>
-      </c>
-      <c r="F100" s="61"/>
-      <c r="G100" s="38"/>
-      <c r="H100" s="38"/>
-      <c r="I100" s="38"/>
-      <c r="J100" s="38"/>
-      <c r="K100" s="38"/>
-      <c r="L100" s="38"/>
-      <c r="M100" s="38"/>
-      <c r="N100" s="38"/>
-      <c r="O100" s="38"/>
-      <c r="P100" s="38"/>
-      <c r="Q100" s="38"/>
+      <c r="B99" s="27" t="s">
+        <v>4</v>
+      </c>
+      <c r="C99" s="237">
+        <f>BS!G32</f>
+        <v>86862.700000000012</v>
+      </c>
+      <c r="D99" s="27"/>
+      <c r="E99" s="27"/>
+      <c r="F99" s="27"/>
+      <c r="G99" s="218">
+        <f t="shared" ref="G99:Q99" si="41">IF(G$4="","",G103+G102)</f>
+        <v>86862.399999999994</v>
+      </c>
+      <c r="H99" s="218">
+        <f t="shared" si="41"/>
+        <v>87340.5</v>
+      </c>
+      <c r="I99" s="218">
+        <f t="shared" si="41"/>
+        <v>87737.299999999988</v>
+      </c>
+      <c r="J99" s="218">
+        <f t="shared" si="41"/>
+        <v>64308.2</v>
+      </c>
+      <c r="K99" s="218">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
+      <c r="L99" s="218">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
+      <c r="M99" s="218">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
+      <c r="N99" s="218">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
+      <c r="O99" s="218" t="str">
+        <f t="shared" si="41"/>
+        <v/>
+      </c>
+      <c r="P99" s="218" t="str">
+        <f t="shared" si="41"/>
+        <v/>
+      </c>
+      <c r="Q99" s="218" t="str">
+        <f t="shared" si="41"/>
+        <v/>
+      </c>
+    </row>
+    <row r="100" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A100" s="10"/>
+      <c r="B100" s="110" t="s">
+        <v>334</v>
+      </c>
+      <c r="C100" s="238">
+        <f>BS!C4</f>
+        <v>5848.8</v>
+      </c>
+      <c r="D100" s="102"/>
+      <c r="E100" s="102"/>
+      <c r="F100" s="102"/>
+      <c r="G100" s="220">
+        <f>IF(G$4="","",Data!D76)</f>
+        <v>213823</v>
+      </c>
+      <c r="H100" s="220">
+        <f>IF(H$4="","",Data!E76)</f>
+        <v>187711</v>
+      </c>
+      <c r="I100" s="220">
+        <f>IF(I$4="","",Data!F76)</f>
+        <v>277338</v>
+      </c>
+      <c r="J100" s="220">
+        <f>IF(J$4="","",Data!G76)</f>
+        <v>0</v>
+      </c>
+      <c r="K100" s="220">
+        <f>IF(K$4="","",Data!H76)</f>
+        <v>0</v>
+      </c>
+      <c r="L100" s="220">
+        <f>IF(L$4="","",Data!I76)</f>
+        <v>0</v>
+      </c>
+      <c r="M100" s="220">
+        <f>IF(M$4="","",Data!J76)</f>
+        <v>0</v>
+      </c>
+      <c r="N100" s="220">
+        <f>IF(N$4="","",Data!K76)</f>
+        <v>0</v>
+      </c>
+      <c r="O100" s="220" t="str">
+        <f>IF(O$4="","",Data!L76)</f>
+        <v/>
+      </c>
+      <c r="P100" s="220" t="str">
+        <f>IF(P$4="","",Data!M76)</f>
+        <v/>
+      </c>
+      <c r="Q100" s="220" t="str">
+        <f>IF(Q$4="","",Data!N76)</f>
+        <v/>
+      </c>
     </row>
     <row r="101" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A101" s="10"/>
-      <c r="B101" s="70" t="s">
-        <v>31</v>
-      </c>
-      <c r="G101" s="115" t="s">
-        <v>347</v>
+      <c r="B101" s="110" t="s">
+        <v>335</v>
+      </c>
+      <c r="C101" s="238">
+        <f>BS!C6+BS!C7</f>
+        <v>67632</v>
+      </c>
+      <c r="D101" s="102"/>
+      <c r="E101" s="102"/>
+      <c r="F101" s="102"/>
+      <c r="G101" s="220">
+        <f>IF(G$4="","",Data!D77)</f>
+        <v>8852611</v>
+      </c>
+      <c r="H101" s="220">
+        <f>IF(H$4="","",Data!E77)</f>
+        <v>8769304</v>
+      </c>
+      <c r="I101" s="220">
+        <f>IF(I$4="","",Data!F77)</f>
+        <v>7321614</v>
+      </c>
+      <c r="J101" s="220">
+        <f>IF(J$4="","",Data!G77)</f>
+        <v>0</v>
+      </c>
+      <c r="K101" s="220">
+        <f>IF(K$4="","",Data!H77)</f>
+        <v>0</v>
+      </c>
+      <c r="L101" s="220">
+        <f>IF(L$4="","",Data!I77)</f>
+        <v>0</v>
+      </c>
+      <c r="M101" s="220">
+        <f>IF(M$4="","",Data!J77)</f>
+        <v>0</v>
+      </c>
+      <c r="N101" s="220">
+        <f>IF(N$4="","",Data!K77)</f>
+        <v>0</v>
+      </c>
+      <c r="O101" s="220" t="str">
+        <f>IF(O$4="","",Data!L77)</f>
+        <v/>
+      </c>
+      <c r="P101" s="220" t="str">
+        <f>IF(P$4="","",Data!M77)</f>
+        <v/>
+      </c>
+      <c r="Q101" s="220" t="str">
+        <f>IF(Q$4="","",Data!N77)</f>
+        <v/>
       </c>
     </row>
     <row r="102" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A102" s="10"/>
       <c r="B102" s="27" t="s">
-        <v>4</v>
+        <v>52</v>
       </c>
       <c r="C102" s="237">
-        <f>BS!G32</f>
-        <v>86862.700000000012</v>
+        <f>BS!G30</f>
+        <v>60481</v>
       </c>
       <c r="D102" s="27"/>
       <c r="E102" s="27"/>
       <c r="F102" s="27"/>
       <c r="G102" s="218">
-        <f t="shared" ref="G102" si="8">IF(G$4="","",G106+G105)</f>
-        <v>86862.399999999994</v>
-      </c>
-      <c r="H102" s="267"/>
-      <c r="I102" s="267"/>
-      <c r="J102" s="267"/>
-      <c r="K102" s="267"/>
-      <c r="L102" s="267"/>
-      <c r="M102" s="267"/>
-      <c r="N102" s="267"/>
-      <c r="O102" s="267"/>
-      <c r="P102" s="267"/>
-      <c r="Q102" s="267"/>
+        <f>Data!C78</f>
+        <v>60481</v>
+      </c>
+      <c r="H102" s="218">
+        <f>Data!D78</f>
+        <v>53980.7</v>
+      </c>
+      <c r="I102" s="218">
+        <f>Data!E78</f>
+        <v>53182.6</v>
+      </c>
+      <c r="J102" s="218">
+        <f>Data!F78</f>
+        <v>32740.6</v>
+      </c>
+      <c r="K102" s="218">
+        <f>Data!G78</f>
+        <v>0</v>
+      </c>
+      <c r="L102" s="218">
+        <f>Data!H78</f>
+        <v>0</v>
+      </c>
+      <c r="M102" s="218">
+        <f>Data!I78</f>
+        <v>0</v>
+      </c>
+      <c r="N102" s="218">
+        <f>Data!J78</f>
+        <v>0</v>
+      </c>
+      <c r="O102" s="218" t="str">
+        <f>Data!K78</f>
+        <v/>
+      </c>
+      <c r="P102" s="218" t="str">
+        <f>Data!L78</f>
+        <v/>
+      </c>
+      <c r="Q102" s="218" t="str">
+        <f>Data!M78</f>
+        <v/>
+      </c>
     </row>
     <row r="103" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A103" s="10"/>
-      <c r="B103" s="110" t="s">
-        <v>338</v>
-      </c>
-      <c r="C103" s="238">
-        <f>BS!C4</f>
-        <v>5848.8</v>
-      </c>
-      <c r="D103" s="102"/>
-      <c r="E103" s="102"/>
-      <c r="F103" s="102"/>
-      <c r="G103" s="220">
-        <f>IF(G$4="","",Data!D76)</f>
-        <v>213823</v>
-      </c>
-      <c r="H103" s="220">
-        <f>IF(H$4="","",Data!E76)</f>
-        <v>187711</v>
-      </c>
-      <c r="I103" s="220">
-        <f>IF(I$4="","",Data!F76)</f>
-        <v>277338</v>
-      </c>
-      <c r="J103" s="220">
-        <f>IF(J$4="","",Data!G76)</f>
-        <v>0</v>
-      </c>
-      <c r="K103" s="220">
-        <f>IF(K$4="","",Data!H76)</f>
-        <v>0</v>
-      </c>
-      <c r="L103" s="220">
-        <f>IF(L$4="","",Data!I76)</f>
-        <v>0</v>
-      </c>
-      <c r="M103" s="220">
-        <f>IF(M$4="","",Data!J76)</f>
-        <v>0</v>
-      </c>
-      <c r="N103" s="220">
-        <f>IF(N$4="","",Data!K76)</f>
-        <v>0</v>
-      </c>
-      <c r="O103" s="220" t="str">
-        <f>IF(O$4="","",Data!L76)</f>
-        <v/>
-      </c>
-      <c r="P103" s="220" t="str">
-        <f>IF(P$4="","",Data!M76)</f>
-        <v/>
-      </c>
-      <c r="Q103" s="220" t="str">
-        <f>IF(Q$4="","",Data!N76)</f>
+      <c r="B103" s="27" t="s">
+        <v>33</v>
+      </c>
+      <c r="C103" s="237">
+        <f>BS!G27</f>
+        <v>26381.700000000012</v>
+      </c>
+      <c r="D103" s="27"/>
+      <c r="E103" s="27"/>
+      <c r="F103" s="27"/>
+      <c r="G103" s="218">
+        <f>Data!C79</f>
+        <v>26381.4</v>
+      </c>
+      <c r="H103" s="218">
+        <f>Data!D79</f>
+        <v>33359.800000000003</v>
+      </c>
+      <c r="I103" s="218">
+        <f>Data!E79</f>
+        <v>34554.699999999997</v>
+      </c>
+      <c r="J103" s="218">
+        <f>Data!F79</f>
+        <v>31567.599999999999</v>
+      </c>
+      <c r="K103" s="218">
+        <f>Data!G79</f>
+        <v>0</v>
+      </c>
+      <c r="L103" s="218">
+        <f>Data!H79</f>
+        <v>0</v>
+      </c>
+      <c r="M103" s="218">
+        <f>Data!I79</f>
+        <v>0</v>
+      </c>
+      <c r="N103" s="218">
+        <f>Data!J79</f>
+        <v>0</v>
+      </c>
+      <c r="O103" s="218" t="str">
+        <f>Data!K79</f>
+        <v/>
+      </c>
+      <c r="P103" s="218" t="str">
+        <f>Data!L79</f>
+        <v/>
+      </c>
+      <c r="Q103" s="218" t="str">
+        <f>Data!M79</f>
         <v/>
       </c>
     </row>
     <row r="104" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A104" s="10"/>
-      <c r="B104" s="110" t="s">
-        <v>339</v>
-      </c>
-      <c r="C104" s="238">
-        <f>BS!C6+BS!C7</f>
-        <v>67632</v>
-      </c>
-      <c r="D104" s="102"/>
-      <c r="E104" s="102"/>
-      <c r="F104" s="102"/>
-      <c r="G104" s="220">
-        <f>IF(G$4="","",Data!D77)</f>
-        <v>8852611</v>
-      </c>
-      <c r="H104" s="220">
-        <f>IF(H$4="","",Data!E77)</f>
-        <v>8769304</v>
-      </c>
-      <c r="I104" s="220">
-        <f>IF(I$4="","",Data!F77)</f>
-        <v>7321614</v>
-      </c>
-      <c r="J104" s="220">
-        <f>IF(J$4="","",Data!G77)</f>
-        <v>0</v>
-      </c>
-      <c r="K104" s="220">
-        <f>IF(K$4="","",Data!H77)</f>
-        <v>0</v>
-      </c>
-      <c r="L104" s="220">
-        <f>IF(L$4="","",Data!I77)</f>
-        <v>0</v>
-      </c>
-      <c r="M104" s="220">
-        <f>IF(M$4="","",Data!J77)</f>
-        <v>0</v>
-      </c>
-      <c r="N104" s="220">
-        <f>IF(N$4="","",Data!K77)</f>
-        <v>0</v>
-      </c>
-      <c r="O104" s="220" t="str">
-        <f>IF(O$4="","",Data!L77)</f>
-        <v/>
-      </c>
-      <c r="P104" s="220" t="str">
-        <f>IF(P$4="","",Data!M77)</f>
-        <v/>
-      </c>
-      <c r="Q104" s="220" t="str">
-        <f>IF(Q$4="","",Data!N77)</f>
-        <v/>
-      </c>
     </row>
     <row r="105" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A105" s="10"/>
-      <c r="B105" s="27" t="s">
-        <v>53</v>
-      </c>
-      <c r="C105" s="237">
-        <f>BS!G30</f>
-        <v>60481</v>
-      </c>
+      <c r="B105" s="105" t="s">
+        <v>344</v>
+      </c>
+      <c r="C105" s="27"/>
       <c r="D105" s="27"/>
       <c r="E105" s="27"/>
       <c r="F105" s="27"/>
-      <c r="G105" s="218">
-        <f>Data!C78</f>
-        <v>60481</v>
-      </c>
-      <c r="H105" s="267"/>
-      <c r="I105" s="267"/>
-      <c r="J105" s="267"/>
-      <c r="K105" s="267"/>
-      <c r="L105" s="267"/>
-      <c r="M105" s="267"/>
-      <c r="N105" s="267"/>
-      <c r="O105" s="267"/>
-      <c r="P105" s="267"/>
-      <c r="Q105" s="267"/>
+      <c r="G105" s="115" t="s">
+        <v>343</v>
+      </c>
+      <c r="H105" s="12"/>
+      <c r="I105" s="12"/>
+      <c r="J105" s="12"/>
+      <c r="K105" s="12"/>
+      <c r="L105" s="12"/>
+      <c r="M105" s="12"/>
+      <c r="N105" s="12"/>
+      <c r="O105" s="12"/>
+      <c r="P105" s="12"/>
+      <c r="Q105" s="12"/>
     </row>
     <row r="106" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A106" s="10"/>
       <c r="B106" s="27" t="s">
-        <v>33</v>
-      </c>
-      <c r="C106" s="237">
-        <f>BS!G27</f>
-        <v>26381.700000000012</v>
+        <v>341</v>
+      </c>
+      <c r="C106" s="112">
+        <f>C100/C$4</f>
+        <v>5.8036265058208601E-2</v>
       </c>
       <c r="D106" s="27"/>
       <c r="E106" s="27"/>
       <c r="F106" s="27"/>
-      <c r="G106" s="218">
-        <f>Data!C79</f>
-        <v>26381.4</v>
-      </c>
-      <c r="H106" s="267"/>
-      <c r="I106" s="267"/>
-      <c r="J106" s="267"/>
-      <c r="K106" s="267"/>
-      <c r="L106" s="267"/>
-      <c r="M106" s="267"/>
-      <c r="N106" s="267"/>
-      <c r="O106" s="267"/>
-      <c r="P106" s="267"/>
-      <c r="Q106" s="267"/>
+      <c r="G106" s="112">
+        <f t="shared" ref="G106:Q106" si="42">IF(G$4="","",G100/G$4)</f>
+        <v>1.9668576895127539</v>
+      </c>
+      <c r="H106" s="112">
+        <f t="shared" si="42"/>
+        <v>1.9824913079662543</v>
+      </c>
+      <c r="I106" s="112">
+        <f t="shared" si="42"/>
+        <v>2.8031579468695957</v>
+      </c>
+      <c r="J106" s="112">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="K106" s="112">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="L106" s="112">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="M106" s="112">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="N106" s="112">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="O106" s="112" t="str">
+        <f t="shared" si="42"/>
+        <v/>
+      </c>
+      <c r="P106" s="112" t="str">
+        <f t="shared" si="42"/>
+        <v/>
+      </c>
+      <c r="Q106" s="112" t="str">
+        <f t="shared" si="42"/>
+        <v/>
+      </c>
     </row>
     <row r="107" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A107" s="10"/>
+      <c r="B107" s="27" t="s">
+        <v>342</v>
+      </c>
+      <c r="C107" s="112">
+        <f>C101/C$4</f>
+        <v>0.67109640924920733</v>
+      </c>
+      <c r="D107" s="27"/>
+      <c r="E107" s="27"/>
+      <c r="F107" s="27"/>
+      <c r="G107" s="112">
+        <f t="shared" ref="G107:Q107" si="43">IF(G$4="","",G101/G$4)</f>
+        <v>81.431024808440569</v>
+      </c>
+      <c r="H107" s="112">
+        <f t="shared" si="43"/>
+        <v>92.616143736455001</v>
+      </c>
+      <c r="I107" s="112">
+        <f t="shared" si="43"/>
+        <v>74.002266072488041</v>
+      </c>
+      <c r="J107" s="112">
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="K107" s="112">
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="L107" s="112">
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="M107" s="112">
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="N107" s="112">
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="O107" s="112" t="str">
+        <f t="shared" si="43"/>
+        <v/>
+      </c>
+      <c r="P107" s="112" t="str">
+        <f t="shared" si="43"/>
+        <v/>
+      </c>
+      <c r="Q107" s="112" t="str">
+        <f t="shared" si="43"/>
+        <v/>
+      </c>
     </row>
     <row r="108" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A108" s="10"/>
-      <c r="B108" s="105" t="s">
-        <v>50</v>
-      </c>
-      <c r="C108" s="60"/>
-      <c r="D108" s="60"/>
-      <c r="E108" s="60"/>
-      <c r="F108" s="60"/>
-      <c r="G108" s="24" t="str">
-        <f>IFERROR(IF(#REF!*G110*(1/#REF!)=G112,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="H108" s="24" t="str">
-        <f>IFERROR(IF(#REF!*H110*(1/#REF!)=H112,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="I108" s="24" t="str">
-        <f>IFERROR(IF(#REF!*I110*(1/#REF!)=I112,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="J108" s="24" t="str">
-        <f>IFERROR(IF(#REF!*J110*(1/#REF!)=J112,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="K108" s="24" t="str">
-        <f>IFERROR(IF(#REF!*K110*(1/#REF!)=K112,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="L108" s="24" t="str">
-        <f>IFERROR(IF(#REF!*L110*(1/#REF!)=L112,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="M108" s="24" t="str">
-        <f>IFERROR(IF(#REF!*M110*(1/#REF!)=M112,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="N108" s="24" t="str">
-        <f>IFERROR(IF(#REF!*N110*(1/#REF!)=N112,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="O108" s="24" t="str">
-        <f>IFERROR(IF(#REF!*O110*(1/#REF!)=O112,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="P108" s="24" t="str">
-        <f>IFERROR(IF(#REF!*P110*(1/#REF!)=P112,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="Q108" s="24" t="str">
-        <f>IFERROR(IF(#REF!*Q110*(1/#REF!)=Q112,"","Error"),"")</f>
-        <v/>
-      </c>
+      <c r="B108" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="C108" s="112">
+        <f>BS!$G$38/C$4</f>
+        <v>0</v>
+      </c>
+      <c r="D108" s="27"/>
+      <c r="E108" s="27"/>
+      <c r="F108" s="27"/>
+      <c r="G108" s="112">
+        <f>BS!$G$38/G$4</f>
+        <v>0</v>
+      </c>
+      <c r="H108" s="264"/>
+      <c r="I108" s="264"/>
+      <c r="J108" s="264"/>
+      <c r="K108" s="264"/>
+      <c r="L108" s="264"/>
+      <c r="M108" s="264"/>
+      <c r="N108" s="264"/>
+      <c r="O108" s="264"/>
+      <c r="P108" s="264"/>
+      <c r="Q108" s="264"/>
     </row>
     <row r="109" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A109" s="10"/>
-      <c r="B109" s="7" t="s">
-        <v>160</v>
-      </c>
-      <c r="C109" s="24">
-        <f>C75</f>
-        <v>8.0617926988698241E-2</v>
-      </c>
-      <c r="G109" s="24">
-        <f>G75</f>
-        <v>8.2646969543660853E-2</v>
-      </c>
-      <c r="H109" s="24">
-        <f>H75</f>
-        <v>7.8954928161344404E-2</v>
-      </c>
-      <c r="I109" s="24">
-        <f>I75</f>
-        <v>8.4254030566710145E-2</v>
-      </c>
-      <c r="J109" s="24">
-        <f>J75</f>
-        <v>0.11667412540369829</v>
-      </c>
-      <c r="K109" s="24">
-        <f>K75</f>
-        <v>7.9286988024838481E-2</v>
-      </c>
-      <c r="L109" s="24">
-        <f>L75</f>
-        <v>9.8070983140041562E-2</v>
-      </c>
-      <c r="M109" s="24">
-        <f>M75</f>
-        <v>8.8803578311053427E-2</v>
-      </c>
-      <c r="N109" s="24">
-        <f>N75</f>
-        <v>9.0068396249426752E-2</v>
-      </c>
-      <c r="O109" s="24" t="str">
-        <f>O75</f>
-        <v/>
-      </c>
-      <c r="P109" s="24" t="str">
-        <f>P75</f>
-        <v/>
-      </c>
-      <c r="Q109" s="24" t="str">
-        <f>Q75</f>
-        <v/>
-      </c>
     </row>
     <row r="110" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B110" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="C110" s="44">
-        <f>C4/C102</f>
+      <c r="A110" s="10"/>
+      <c r="B110" s="105" t="s">
+        <v>50</v>
+      </c>
+      <c r="C110" s="60"/>
+      <c r="D110" s="60"/>
+      <c r="E110" s="60"/>
+      <c r="F110" s="60"/>
+      <c r="G110" s="24" t="str">
+        <f>IFERROR(IF(#REF!*G112*(1/#REF!)=G114,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="H110" s="24" t="str">
+        <f>IFERROR(IF(#REF!*H112*(1/#REF!)=H114,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="I110" s="24" t="str">
+        <f>IFERROR(IF(#REF!*I112*(1/#REF!)=I114,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="J110" s="24" t="str">
+        <f>IFERROR(IF(#REF!*J112*(1/#REF!)=J114,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="K110" s="24" t="str">
+        <f>IFERROR(IF(#REF!*K112*(1/#REF!)=K114,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="L110" s="24" t="str">
+        <f>IFERROR(IF(#REF!*L112*(1/#REF!)=L114,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="M110" s="24" t="str">
+        <f>IFERROR(IF(#REF!*M112*(1/#REF!)=M114,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="N110" s="24" t="str">
+        <f>IFERROR(IF(#REF!*N112*(1/#REF!)=N114,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="O110" s="24" t="str">
+        <f>IFERROR(IF(#REF!*O112*(1/#REF!)=O114,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="P110" s="24" t="str">
+        <f>IFERROR(IF(#REF!*P112*(1/#REF!)=P114,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="Q110" s="24" t="str">
+        <f>IFERROR(IF(#REF!*Q112*(1/#REF!)=Q114,"","Error"),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="111" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A111" s="10"/>
+      <c r="B111" s="7" t="s">
+        <v>346</v>
+      </c>
+      <c r="C111" s="24">
+        <f>C80</f>
+        <v>7.4769241209243581E-2</v>
+      </c>
+      <c r="G111" s="24">
+        <f t="shared" ref="G111:Q111" si="44">G80</f>
+        <v>3.3464064160603729E-17</v>
+      </c>
+      <c r="H111" s="24">
+        <f t="shared" si="44"/>
+        <v>1.1100033374029537E-3</v>
+      </c>
+      <c r="I111" s="24">
+        <f t="shared" si="44"/>
+        <v>1.6939953122015188E-3</v>
+      </c>
+      <c r="J111" s="24">
+        <f t="shared" si="44"/>
+        <v>2.1335788540529422E-3</v>
+      </c>
+      <c r="K111" s="24">
+        <f t="shared" si="44"/>
+        <v>1.4466756415768551E-3</v>
+      </c>
+      <c r="L111" s="24">
+        <f t="shared" si="44"/>
+        <v>1.6081391040324987E-3</v>
+      </c>
+      <c r="M111" s="24">
+        <f t="shared" si="44"/>
+        <v>1.8324306414859656E-3</v>
+      </c>
+      <c r="N111" s="24">
+        <f t="shared" si="44"/>
+        <v>1.8694324379701563E-3</v>
+      </c>
+      <c r="O111" s="24" t="str">
+        <f t="shared" si="44"/>
+        <v/>
+      </c>
+      <c r="P111" s="24" t="str">
+        <f t="shared" si="44"/>
+        <v/>
+      </c>
+      <c r="Q111" s="24" t="str">
+        <f t="shared" si="44"/>
+        <v/>
+      </c>
+    </row>
+    <row r="112" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B112" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="C112" s="44">
+        <f>C4/C99</f>
         <v>1.1602030177126275</v>
       </c>
-      <c r="G110" s="44">
-        <f>IF(G4="","",G4/G102)</f>
+      <c r="G112" s="44">
+        <f t="shared" ref="G112:Q112" si="45">IF(G4="","",G4/G99)</f>
         <v>1.2515541822468641</v>
       </c>
-      <c r="H110" s="44" t="e">
-        <f>IF(H4="","",H4/H102)</f>
+      <c r="H112" s="44">
+        <f t="shared" si="45"/>
+        <v>1.084083558028635</v>
+      </c>
+      <c r="I112" s="44">
+        <f t="shared" si="45"/>
+        <v>1.1276583619509606</v>
+      </c>
+      <c r="J112" s="44">
+        <f t="shared" si="45"/>
+        <v>1.0910552620039125</v>
+      </c>
+      <c r="K112" s="44" t="e">
+        <f t="shared" si="45"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I110" s="44" t="e">
-        <f>IF(I4="","",I4/I102)</f>
+      <c r="L112" s="44" t="e">
+        <f t="shared" si="45"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J110" s="44" t="e">
-        <f>IF(J4="","",J4/J102)</f>
+      <c r="M112" s="44" t="e">
+        <f t="shared" si="45"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="K110" s="44" t="e">
-        <f>IF(K4="","",K4/K102)</f>
+      <c r="N112" s="44" t="e">
+        <f t="shared" si="45"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L110" s="44" t="e">
-        <f>IF(L4="","",L4/L102)</f>
+      <c r="O112" s="44" t="str">
+        <f t="shared" si="45"/>
+        <v/>
+      </c>
+      <c r="P112" s="44" t="str">
+        <f t="shared" si="45"/>
+        <v/>
+      </c>
+      <c r="Q112" s="44" t="str">
+        <f t="shared" si="45"/>
+        <v/>
+      </c>
+    </row>
+    <row r="113" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B113" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="C113" s="15">
+        <f>C99/C103</f>
+        <v>3.2925361140487523</v>
+      </c>
+      <c r="D113" s="11"/>
+      <c r="E113" s="11"/>
+      <c r="F113" s="11"/>
+      <c r="G113" s="15">
+        <f t="shared" ref="G113:Q113" si="46">IF(G$4="","",G99/G103)</f>
+        <v>3.2925621839629433</v>
+      </c>
+      <c r="H113" s="15">
+        <f t="shared" si="46"/>
+        <v>2.6181361998573132</v>
+      </c>
+      <c r="I113" s="15">
+        <f t="shared" si="46"/>
+        <v>2.5390844081991739</v>
+      </c>
+      <c r="J113" s="15">
+        <f t="shared" si="46"/>
+        <v>2.0371583522345698</v>
+      </c>
+      <c r="K113" s="15" t="e">
+        <f t="shared" si="46"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="M110" s="44" t="e">
-        <f>IF(M4="","",M4/M102)</f>
+      <c r="L113" s="15" t="e">
+        <f t="shared" si="46"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N110" s="44" t="e">
-        <f>IF(N4="","",N4/N102)</f>
+      <c r="M113" s="15" t="e">
+        <f t="shared" si="46"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O110" s="44" t="str">
-        <f>IF(O4="","",O4/O102)</f>
-        <v/>
-      </c>
-      <c r="P110" s="44" t="str">
-        <f>IF(P4="","",P4/P102)</f>
-        <v/>
-      </c>
-      <c r="Q110" s="44" t="str">
-        <f>IF(Q4="","",Q4/Q102)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="111" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B111" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="C111" s="15">
-        <f>C102/C106</f>
-        <v>3.2925361140487523</v>
-      </c>
-      <c r="D111" s="11"/>
-      <c r="E111" s="11"/>
-      <c r="F111" s="11"/>
-      <c r="G111" s="15">
-        <f t="shared" ref="G111:Q111" si="9">IF(G$4="","",G102/G106)</f>
-        <v>3.2925621839629433</v>
-      </c>
-      <c r="H111" s="15" t="e">
-        <f t="shared" si="9"/>
+      <c r="N113" s="15" t="e">
+        <f t="shared" si="46"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I111" s="15" t="e">
-        <f t="shared" si="9"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J111" s="15" t="e">
-        <f t="shared" si="9"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K111" s="15" t="e">
-        <f t="shared" si="9"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L111" s="15" t="e">
-        <f t="shared" si="9"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M111" s="15" t="e">
-        <f t="shared" si="9"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N111" s="15" t="e">
-        <f t="shared" si="9"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O111" s="15" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="P111" s="15" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="Q111" s="15" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="112" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A112" s="10"/>
-      <c r="B112" s="80" t="s">
-        <v>51</v>
-      </c>
-      <c r="C112" s="121">
-        <f>C8/C106</f>
-        <v>0.30796131431915263</v>
-      </c>
-      <c r="D112" s="122"/>
-      <c r="E112" s="122"/>
-      <c r="F112" s="122"/>
-      <c r="G112" s="121">
-        <f>IF(G$4="","",G8/G106)</f>
-        <v>0.34057328269159343</v>
-      </c>
-      <c r="H112" s="121" t="e">
-        <f>IF(H$4="","",H8/H106)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I112" s="121" t="e">
-        <f>IF(I$4="","",I8/I106)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J112" s="121" t="e">
-        <f>IF(J$4="","",J8/J106)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K112" s="121" t="e">
-        <f>IF(K$4="","",K8/K106)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L112" s="121" t="e">
-        <f>IF(L$4="","",L8/L106)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M112" s="121" t="e">
-        <f>IF(M$4="","",M8/M106)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N112" s="121" t="e">
-        <f>IF(N$4="","",N8/N106)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O112" s="121" t="str">
-        <f>IF(O$4="","",O8/O106)</f>
-        <v/>
-      </c>
-      <c r="P112" s="121" t="str">
-        <f>IF(P$4="","",P8/P106)</f>
-        <v/>
-      </c>
-      <c r="Q112" s="121" t="str">
-        <f>IF(Q$4="","",Q8/Q106)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="113" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A113" s="10"/>
-      <c r="B113" s="28"/>
-      <c r="C113" s="68"/>
-      <c r="D113" s="28"/>
-      <c r="E113" s="77"/>
-      <c r="F113" s="28"/>
-      <c r="G113" s="12"/>
-      <c r="H113" s="12"/>
-      <c r="I113" s="12"/>
-      <c r="J113" s="12"/>
-      <c r="K113" s="12"/>
-      <c r="L113" s="12"/>
-      <c r="M113" s="12"/>
-      <c r="N113" s="12"/>
-      <c r="O113" s="12"/>
-      <c r="P113" s="12"/>
-      <c r="Q113" s="12"/>
+      <c r="O113" s="15" t="str">
+        <f t="shared" si="46"/>
+        <v/>
+      </c>
+      <c r="P113" s="15" t="str">
+        <f t="shared" si="46"/>
+        <v/>
+      </c>
+      <c r="Q113" s="15" t="str">
+        <f t="shared" si="46"/>
+        <v/>
+      </c>
     </row>
     <row r="114" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A114" s="10"/>
-      <c r="B114" s="214" t="s">
-        <v>290</v>
-      </c>
-      <c r="C114" s="215"/>
-      <c r="D114" s="28"/>
-      <c r="E114" s="77"/>
-      <c r="F114" s="28"/>
-      <c r="G114" s="12"/>
-      <c r="H114" s="12"/>
-      <c r="I114" s="12"/>
-      <c r="J114" s="12"/>
-      <c r="K114" s="12"/>
-      <c r="L114" s="12"/>
-      <c r="M114" s="12"/>
-      <c r="N114" s="12"/>
-      <c r="O114" s="12"/>
-      <c r="P114" s="12"/>
-      <c r="Q114" s="12"/>
+      <c r="B114" s="80" t="s">
+        <v>347</v>
+      </c>
+      <c r="C114" s="121">
+        <f>C8/C103</f>
+        <v>0.30796131431915263</v>
+      </c>
+      <c r="D114" s="122"/>
+      <c r="E114" s="122"/>
+      <c r="F114" s="122"/>
+      <c r="G114" s="121">
+        <f t="shared" ref="G114:Q114" si="47">IF(G$4="","",G8/G103)</f>
+        <v>0.34057328269159343</v>
+      </c>
+      <c r="H114" s="121">
+        <f t="shared" si="47"/>
+        <v>0.22409606772222845</v>
+      </c>
+      <c r="I114" s="121">
+        <f t="shared" si="47"/>
+        <v>0.2412378055662471</v>
+      </c>
+      <c r="J114" s="121">
+        <f t="shared" si="47"/>
+        <v>0.25932601781573533</v>
+      </c>
+      <c r="K114" s="121" t="e">
+        <f t="shared" si="47"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L114" s="121" t="e">
+        <f t="shared" si="47"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M114" s="121" t="e">
+        <f t="shared" si="47"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N114" s="121" t="e">
+        <f t="shared" si="47"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O114" s="121" t="str">
+        <f t="shared" si="47"/>
+        <v/>
+      </c>
+      <c r="P114" s="121" t="str">
+        <f t="shared" si="47"/>
+        <v/>
+      </c>
+      <c r="Q114" s="121" t="str">
+        <f t="shared" si="47"/>
+        <v/>
+      </c>
     </row>
     <row r="115" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A115" s="10"/>
-      <c r="B115" s="28" t="str">
-        <f>"FCFE per share ("&amp;Market_currency&amp;")"</f>
-        <v>FCFE per share (HKD)</v>
-      </c>
-      <c r="C115" s="213">
-        <f>C19*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>0.55938852458884103</v>
-      </c>
+      <c r="B115" s="28"/>
+      <c r="C115" s="68"/>
       <c r="D115" s="28"/>
       <c r="E115" s="77"/>
       <c r="F115" s="28"/>
-      <c r="G115" s="213">
-        <f>IF(G$4="","",G19*$C$3/Common_Shares*Exchange_Rate)</f>
+      <c r="G115" s="12"/>
+      <c r="H115" s="12"/>
+      <c r="I115" s="12"/>
+      <c r="J115" s="12"/>
+      <c r="K115" s="12"/>
+      <c r="L115" s="12"/>
+      <c r="M115" s="12"/>
+      <c r="N115" s="12"/>
+      <c r="O115" s="12"/>
+      <c r="P115" s="12"/>
+      <c r="Q115" s="12"/>
+    </row>
+    <row r="116" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A116" s="10"/>
+      <c r="B116" s="59" t="s">
+        <v>348</v>
+      </c>
+      <c r="C116" s="59"/>
+      <c r="D116" s="61"/>
+      <c r="E116" s="72" t="s">
+        <v>118</v>
+      </c>
+      <c r="F116" s="61"/>
+      <c r="G116" s="38"/>
+      <c r="H116" s="38"/>
+      <c r="I116" s="38"/>
+      <c r="J116" s="38"/>
+      <c r="K116" s="38"/>
+      <c r="L116" s="38"/>
+      <c r="M116" s="38"/>
+      <c r="N116" s="38"/>
+      <c r="O116" s="38"/>
+      <c r="P116" s="38"/>
+      <c r="Q116" s="38"/>
+    </row>
+    <row r="117" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A117" s="10"/>
+      <c r="B117" s="214" t="s">
+        <v>286</v>
+      </c>
+      <c r="C117" s="215"/>
+      <c r="D117" s="28"/>
+      <c r="E117" s="77"/>
+      <c r="F117" s="28"/>
+      <c r="G117" s="12"/>
+      <c r="H117" s="12"/>
+      <c r="I117" s="12"/>
+      <c r="J117" s="12"/>
+      <c r="K117" s="12"/>
+      <c r="L117" s="12"/>
+      <c r="M117" s="12"/>
+      <c r="N117" s="12"/>
+      <c r="O117" s="12"/>
+      <c r="P117" s="12"/>
+      <c r="Q117" s="12"/>
+    </row>
+    <row r="118" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A118" s="10"/>
+      <c r="B118" s="28" t="str">
+        <f>"After-tax Profit per share ("&amp;Market_currency&amp;")"</f>
+        <v>After-tax Profit per share (HKD)</v>
+      </c>
+      <c r="C118" s="213">
+        <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
+        <v>0.55938852458884103</v>
+      </c>
+      <c r="D118" s="28"/>
+      <c r="E118" s="77"/>
+      <c r="F118" s="28"/>
+      <c r="G118" s="213">
+        <f t="shared" ref="G118:Q118" si="48">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
         <v>-1.0803248239380553E-2</v>
       </c>
-      <c r="H115" s="213">
-        <f>IF(H$4="","",H19*$C$3/Common_Shares*Exchange_Rate)</f>
+      <c r="H118" s="213">
+        <f t="shared" si="48"/>
         <v>-3.7847286426728153E-16</v>
       </c>
-      <c r="I115" s="213">
-        <f>IF(I$4="","",I19*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>0</v>
-      </c>
-      <c r="J115" s="213">
-        <f>IF(J$4="","",J19*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>0</v>
-      </c>
-      <c r="K115" s="213">
-        <f>IF(K$4="","",K19*$C$3/Common_Shares*Exchange_Rate)</f>
+      <c r="I118" s="213">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
+      <c r="J118" s="213">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
+      <c r="K118" s="213">
+        <f t="shared" si="48"/>
         <v>-1.991962443512008E-17</v>
       </c>
-      <c r="L115" s="213">
-        <f>IF(L$4="","",L19*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>0</v>
-      </c>
-      <c r="M115" s="213">
-        <f>IF(M$4="","",M19*$C$3/Common_Shares*Exchange_Rate)</f>
+      <c r="L118" s="213">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
+      <c r="M118" s="213">
+        <f t="shared" si="48"/>
         <v>3.6993588236651581E-17</v>
       </c>
-      <c r="N115" s="213">
-        <f>IF(N$4="","",N19*$C$3/Common_Shares*Exchange_Rate)</f>
+      <c r="N118" s="213">
+        <f t="shared" si="48"/>
         <v>-3.5570757919857286E-17</v>
       </c>
-      <c r="O115" s="213" t="str">
-        <f>IF(O$4="","",O19*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v/>
-      </c>
-      <c r="P115" s="213" t="str">
-        <f>IF(P$4="","",P19*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v/>
-      </c>
-      <c r="Q115" s="213" t="str">
-        <f>IF(Q$4="","",Q19*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="116" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A116" s="10"/>
-      <c r="B116" s="28" t="s">
-        <v>167</v>
-      </c>
-      <c r="C116" s="88">
-        <f>C115/Market_Price</f>
+      <c r="O118" s="213" t="str">
+        <f t="shared" si="48"/>
+        <v/>
+      </c>
+      <c r="P118" s="213" t="str">
+        <f t="shared" si="48"/>
+        <v/>
+      </c>
+      <c r="Q118" s="213" t="str">
+        <f t="shared" si="48"/>
+        <v/>
+      </c>
+    </row>
+    <row r="119" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A119" s="10"/>
+      <c r="B119" s="28" t="s">
+        <v>345</v>
+      </c>
+      <c r="C119" s="88">
+        <f>C118/Market_Price</f>
         <v>6.174266275815022E-2</v>
       </c>
-      <c r="D116" s="28"/>
-      <c r="E116" s="77"/>
-      <c r="F116" s="28"/>
-      <c r="G116" s="88">
-        <f>IF(G$4="","",G115/Market_Price)</f>
+      <c r="D119" s="28"/>
+      <c r="E119" s="77"/>
+      <c r="F119" s="28"/>
+      <c r="G119" s="88">
+        <f t="shared" ref="G119" si="49">IF(G$4="","",G118/Market_Price)</f>
         <v>-1.192411505450392E-3</v>
       </c>
-      <c r="H116" s="88">
-        <f>IF(H$4="","",H115/Market_Price)</f>
+      <c r="H119" s="88">
+        <f t="shared" ref="H119" si="50">IF(H$4="","",H118/Market_Price)</f>
         <v>-4.1774046828618267E-17</v>
       </c>
-      <c r="I116" s="88">
-        <f>IF(I$4="","",I115/Market_Price)</f>
-        <v>0</v>
-      </c>
-      <c r="J116" s="88">
-        <f>IF(J$4="","",J115/Market_Price)</f>
-        <v>0</v>
-      </c>
-      <c r="K116" s="88">
-        <f>IF(K$4="","",K115/Market_Price)</f>
+      <c r="I119" s="88">
+        <f t="shared" ref="I119" si="51">IF(I$4="","",I118/Market_Price)</f>
+        <v>0</v>
+      </c>
+      <c r="J119" s="88">
+        <f t="shared" ref="J119" si="52">IF(J$4="","",J118/Market_Price)</f>
+        <v>0</v>
+      </c>
+      <c r="K119" s="88">
+        <f t="shared" ref="K119" si="53">IF(K$4="","",K118/Market_Price)</f>
         <v>-2.1986340436114879E-18</v>
       </c>
-      <c r="L116" s="88">
-        <f>IF(L$4="","",L115/Market_Price)</f>
-        <v>0</v>
-      </c>
-      <c r="M116" s="88">
-        <f>IF(M$4="","",M115/Market_Price)</f>
+      <c r="L119" s="88">
+        <f t="shared" ref="L119" si="54">IF(L$4="","",L118/Market_Price)</f>
+        <v>0</v>
+      </c>
+      <c r="M119" s="88">
+        <f t="shared" ref="M119" si="55">IF(M$4="","",M118/Market_Price)</f>
         <v>4.0831775095641922E-18</v>
       </c>
-      <c r="N116" s="88">
-        <f>IF(N$4="","",N115/Market_Price)</f>
+      <c r="N119" s="88">
+        <f t="shared" ref="N119" si="56">IF(N$4="","",N118/Market_Price)</f>
         <v>-3.9261322207347991E-18</v>
       </c>
-      <c r="O116" s="88" t="str">
-        <f>IF(O$4="","",O115/Market_Price)</f>
-        <v/>
-      </c>
-      <c r="P116" s="88" t="str">
-        <f>IF(P$4="","",P115/Market_Price)</f>
-        <v/>
-      </c>
-      <c r="Q116" s="88" t="str">
-        <f>IF(Q$4="","",Q115/Market_Price)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="117" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="118" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="119" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+      <c r="O119" s="88" t="str">
+        <f t="shared" ref="O119" si="57">IF(O$4="","",O118/Market_Price)</f>
+        <v/>
+      </c>
+      <c r="P119" s="88" t="str">
+        <f t="shared" ref="P119" si="58">IF(P$4="","",P118/Market_Price)</f>
+        <v/>
+      </c>
+      <c r="Q119" s="88" t="str">
+        <f t="shared" ref="Q119" si="59">IF(Q$4="","",Q118/Market_Price)</f>
+        <v/>
+      </c>
+    </row>
     <row r="120" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="121" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="122" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
@@ -10848,9 +11073,12 @@
     <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
-  <conditionalFormatting sqref="G15:Q16 G23:Q24 G34:Q34 G4:Q13">
+  <conditionalFormatting sqref="G4:Q13 G15:Q16 G23:Q24 G34:Q34">
     <cfRule type="expression" dxfId="2" priority="2">
       <formula>ISBLANK(G4)</formula>
     </cfRule>
@@ -10899,7 +11127,7 @@
     </row>
     <row r="2" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B2" s="92" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="C2" s="38"/>
       <c r="D2" s="38"/>
@@ -10910,19 +11138,19 @@
     </row>
     <row r="3" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="16" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="C3" s="242" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="D3" s="243" t="s">
         <v>39</v>
       </c>
       <c r="F3" s="16" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="G3" s="242" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="H3" s="243" t="s">
         <v>39</v>
@@ -10941,7 +11169,7 @@
       </c>
       <c r="E4" s="26"/>
       <c r="F4" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G4" s="20">
         <v>3839.3</v>
@@ -10983,7 +11211,7 @@
       </c>
       <c r="E6" s="26"/>
       <c r="F6" s="4" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="G6" s="20">
         <v>1.5</v>
@@ -10994,7 +11222,7 @@
     </row>
     <row r="7" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C7" s="20">
         <v>0</v>
@@ -11004,7 +11232,7 @@
       </c>
       <c r="E7" s="26"/>
       <c r="F7" s="4" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="G7" s="20">
         <v>0</v>
@@ -11015,7 +11243,7 @@
     </row>
     <row r="8" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B8" s="1" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="C8" s="20">
         <v>0</v>
@@ -11025,7 +11253,7 @@
       </c>
       <c r="E8" s="26"/>
       <c r="F8" s="1" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="G8" s="20">
         <v>0</v>
@@ -11046,7 +11274,7 @@
       </c>
       <c r="E9" s="26"/>
       <c r="F9" s="4" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="G9" s="20">
         <v>0</v>
@@ -11079,7 +11307,7 @@
     </row>
     <row r="12" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B12" s="93" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C12" s="94">
         <f>SUM(C4:C11)</f>
@@ -11090,7 +11318,7 @@
         <v>37327.35</v>
       </c>
       <c r="F12" s="93" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G12" s="94">
         <f>SUM(G4:G9)</f>
@@ -11108,19 +11336,19 @@
     </row>
     <row r="14" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B14" s="16" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="C14" s="242" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="D14" s="243" t="s">
         <v>39</v>
       </c>
       <c r="F14" s="16" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="G14" s="242" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="H14" s="243" t="s">
         <v>39</v>
@@ -11128,7 +11356,7 @@
     </row>
     <row r="15" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B15" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C15" s="20">
         <v>4.8</v>
@@ -11137,7 +11365,7 @@
         <v>0.4</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G15" s="20">
         <v>0</v>
@@ -11158,7 +11386,7 @@
         <v>0.5</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="G16" s="20">
         <v>0</v>
@@ -11169,7 +11397,7 @@
     </row>
     <row r="17" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B17" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C17" s="20">
         <v>0</v>
@@ -11178,7 +11406,7 @@
         <v>0.6</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="G17" s="20">
         <v>63.2</v>
@@ -11189,7 +11417,7 @@
     </row>
     <row r="18" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B18" s="4" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="C18" s="20">
         <v>0</v>
@@ -11198,7 +11426,7 @@
         <v>0.6</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="G18" s="20">
         <f>41.5+40</f>
@@ -11220,7 +11448,7 @@
         <v>0.1</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="G19" s="20">
         <v>0</v>
@@ -11240,7 +11468,7 @@
         <v>0.05</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="G20" s="20">
         <v>0</v>
@@ -11260,7 +11488,7 @@
         <v>0.05</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="G21" s="20">
         <v>387</v>
@@ -11291,7 +11519,7 @@
         <v>0</v>
       </c>
       <c r="F23" s="93" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G23" s="94">
         <f>SUM(G15:G21)</f>
@@ -11304,7 +11532,7 @@
     </row>
     <row r="24" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B24" s="93" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C24" s="94">
         <f>SUM(C15:C23)</f>
@@ -11317,16 +11545,16 @@
     </row>
     <row r="26" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B26" s="16" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="C26" s="242" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="F26" s="244" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="G26" s="245" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="H26" s="246" t="s">
         <v>39</v>
@@ -11360,7 +11588,7 @@
         <v>662.5</v>
       </c>
       <c r="F28" s="249" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G28" s="216">
         <v>1036.4000000000001</v>
@@ -11375,7 +11603,7 @@
         <v>0</v>
       </c>
       <c r="F29" s="250" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G29" s="14">
         <f>G27-G28</f>
@@ -11404,14 +11632,14 @@
     </row>
     <row r="31" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B31" s="93" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="C31" s="94">
         <f>SUM(C27:C30)</f>
         <v>27827.199999999997</v>
       </c>
       <c r="F31" s="250" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G31" s="251">
         <f>C31+C40</f>
@@ -11428,7 +11656,7 @@
         <v>30241.600000000006</v>
       </c>
       <c r="F32" s="252" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G32" s="253">
         <f>G35+G40</f>
@@ -11454,10 +11682,10 @@
       <c r="B34" s="96"/>
       <c r="C34" s="97"/>
       <c r="F34" s="256" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="G34" s="257" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="H34" s="258" t="s">
         <v>39</v>
@@ -11465,10 +11693,10 @@
     </row>
     <row r="35" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B35" s="16" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="C35" s="242" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="F35" s="259" t="s">
         <v>34</v>
@@ -11490,7 +11718,7 @@
         <v>1297.9000000000001</v>
       </c>
       <c r="F36" s="250" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="G36" s="251">
         <f>C4+C15</f>
@@ -11506,7 +11734,7 @@
         <v>515.70000000000005</v>
       </c>
       <c r="F37" s="250" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="G37" s="251">
         <f>C6</f>
@@ -11522,7 +11750,7 @@
         <v>0</v>
       </c>
       <c r="F38" s="250" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="G38" s="251">
         <f>C7+C17</f>
@@ -11538,7 +11766,7 @@
         <v>0</v>
       </c>
       <c r="F39" s="250" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G39" s="251">
         <f>C7+C17+C19+C20</f>
@@ -11551,14 +11779,14 @@
     </row>
     <row r="40" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B40" s="93" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="C40" s="94">
         <f>SUM(C36:C39)</f>
         <v>1813.6000000000001</v>
       </c>
       <c r="F40" s="259" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="G40" s="253">
         <f>G12+G23</f>
@@ -11578,7 +11806,7 @@
         <v>598.59999999999968</v>
       </c>
       <c r="F41" s="250" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="G41" s="251">
         <f>C69</f>
@@ -11597,7 +11825,7 @@
         <v>2412.1999999999998</v>
       </c>
       <c r="F42" s="261" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="G42" s="262">
         <f>C75</f>
@@ -11610,7 +11838,7 @@
     </row>
     <row r="44" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B44" s="92" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C44" s="38"/>
       <c r="D44" s="38"/>
@@ -11621,16 +11849,16 @@
     </row>
     <row r="45" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B45" s="16" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="C45" s="183" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="D45" s="183" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="F45" s="118" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="46" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -11649,7 +11877,7 @@
     </row>
     <row r="47" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B47" s="1" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="C47" s="107">
         <f>G28/G29</f>
@@ -11662,19 +11890,19 @@
     </row>
     <row r="49" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B49" s="184" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="C49" s="115" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D49" s="115" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="E49" s="2"/>
     </row>
     <row r="50" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B50" s="8" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C50" s="113">
         <f>G31/Normalized_FCF!C8</f>
@@ -11687,7 +11915,7 @@
     </row>
     <row r="51" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B51" s="1" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="C51" s="241"/>
       <c r="D51" s="170">
@@ -11697,7 +11925,7 @@
     </row>
     <row r="52" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B52" s="1" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C52" s="241"/>
       <c r="D52" s="107">
@@ -11707,18 +11935,18 @@
     </row>
     <row r="54" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B54" s="184" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="C54" s="115" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D54" s="115" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="55" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B55" s="1" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="C55" s="107">
         <f>Normalized_FCF!C8/G35</f>
@@ -11731,7 +11959,7 @@
     </row>
     <row r="56" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B56" s="1" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="C56" s="107">
         <f>Normalized_FCF!C11/G40</f>
@@ -11744,18 +11972,18 @@
     </row>
     <row r="58" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B58" s="184" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="C58" s="115" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D58" s="115" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="59" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B59" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C59" s="116"/>
       <c r="D59" s="24">
@@ -11763,12 +11991,12 @@
         <v>0</v>
       </c>
       <c r="F59" s="18" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="60" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B60" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C60" s="116"/>
       <c r="D60" s="107">
@@ -11778,7 +12006,7 @@
     </row>
     <row r="63" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B63" s="92" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="C63" s="38"/>
       <c r="D63" s="38"/>
@@ -11789,15 +12017,15 @@
     </row>
     <row r="64" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B64" s="16" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="C64" s="183" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
     </row>
     <row r="65" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B65" s="125" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="C65" s="21">
         <f>G4+G5+G15</f>
@@ -11806,7 +12034,7 @@
     </row>
     <row r="66" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B66" s="125" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="C66" s="21">
         <f>G6+G16</f>
@@ -11815,7 +12043,7 @@
     </row>
     <row r="67" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B67" s="125" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="C67" s="21">
         <f>G18</f>
@@ -11824,7 +12052,7 @@
     </row>
     <row r="68" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B68" s="125" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="C68" s="21">
         <f>G8+G20</f>
@@ -11833,7 +12061,7 @@
     </row>
     <row r="69" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B69" s="93" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="C69" s="94">
         <f>SUM(C65:C68)</f>
@@ -11842,18 +12070,18 @@
     </row>
     <row r="71" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B71" s="16" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="C71" s="183" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="D71" s="183" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
     </row>
     <row r="72" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B72" s="125" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="C72" s="21">
         <f>G7+G17</f>
@@ -11866,7 +12094,7 @@
     </row>
     <row r="73" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B73" s="125" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="C73" s="21">
         <f>G19</f>
@@ -11879,7 +12107,7 @@
     </row>
     <row r="74" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B74" s="125" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="C74" s="21">
         <f>G9+G21</f>
@@ -11892,7 +12120,7 @@
     </row>
     <row r="75" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B75" s="93" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="C75" s="94">
         <f>SUM(C72:C74)</f>
@@ -11919,7 +12147,7 @@
   <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="6.1328125" customWidth="1"/>
-    <col min="2" max="2" width="22.6640625" customWidth="1"/>
+    <col min="2" max="2" width="24.3984375" customWidth="1"/>
     <col min="3" max="6" width="20.6640625" customWidth="1"/>
     <col min="7" max="7" width="5.6640625" customWidth="1"/>
     <col min="8" max="8" width="56.796875" bestFit="1" customWidth="1"/>
@@ -11927,32 +12155,32 @@
   <sheetData>
     <row r="2" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B2" s="37" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="C2" s="38"/>
       <c r="D2" s="38"/>
       <c r="E2" s="38"/>
       <c r="F2" s="38"/>
       <c r="H2" s="153" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="3" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B3" s="131" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="C3" s="127">
         <f>Normalized_FCF!C3</f>
         <v>1000000</v>
       </c>
       <c r="E3" s="131" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="H3" s="143"/>
     </row>
     <row r="4" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B4" s="119" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="C4" s="132">
         <f>Normalized_FCF!C19</f>
@@ -11963,7 +12191,7 @@
         <v>HKD</v>
       </c>
       <c r="E4" s="119" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="F4" s="157">
         <v>0</v>
@@ -11972,43 +12200,42 @@
     </row>
     <row r="5" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B5" s="171" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="C5" s="157">
         <f>Thesis!C37</f>
         <v>0.1</v>
       </c>
       <c r="E5" s="171" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="H5" s="143"/>
     </row>
     <row r="6" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B6" s="173" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="C6" s="239">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
         <v>55870.253525336717</v>
       </c>
       <c r="E6" s="171" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="H6" s="143"/>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B7" s="171" t="s">
-        <v>214</v>
+        <v>349</v>
       </c>
       <c r="C7" s="240">
-        <f>BS!G31</f>
-        <v>29640.799999999996</v>
+        <v>26185.429999999997</v>
       </c>
       <c r="H7" s="143"/>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B8" s="171" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="C8" s="240">
         <f>BS!H42</f>
@@ -12018,11 +12245,11 @@
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B9" s="173" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="C9" s="239">
         <f>C6-C7+C8</f>
-        <v>26306.07352533672</v>
+        <v>29761.443525336719</v>
       </c>
       <c r="D9" t="str">
         <f>Reporting_currency</f>
@@ -12032,7 +12259,7 @@
     </row>
     <row r="10" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B10" s="173" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="C10" s="208">
         <f>Exchange_Rate</f>
@@ -12042,11 +12269,11 @@
     </row>
     <row r="11" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B11" s="172" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C11" s="134">
         <f>(C9*C3)/Common_Shares*C10</f>
-        <v>2.633837279866718</v>
+        <v>2.9797985390781143</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -12059,7 +12286,7 @@
     </row>
     <row r="13" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B13" s="37" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="C13" s="38"/>
       <c r="D13" s="38"/>
@@ -12069,13 +12296,13 @@
     </row>
     <row r="14" spans="2:8" ht="13.15" x14ac:dyDescent="0.35">
       <c r="B14" s="142" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="H14" s="143"/>
     </row>
     <row r="15" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B15" s="176" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="C15" s="188">
         <f>Scenarios!C25</f>
@@ -12085,7 +12312,7 @@
     </row>
     <row r="16" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B16" s="141" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="C16" s="189">
         <f>Scenarios!C24</f>
@@ -12095,11 +12322,11 @@
     </row>
     <row r="17" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B17" s="177" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="C17" s="163">
         <f>(F51-C7)/Common_Shares*C3</f>
-        <v>8.2533716119364087</v>
+        <v>8.599332871147805</v>
       </c>
       <c r="D17" t="str">
         <f>IF(ROUND(C17,1)=ROUND(Scenarios!C29,1),"equals Market Price","a Current Projection")</f>
@@ -12112,19 +12339,19 @@
     </row>
     <row r="19" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B19" s="151" t="s">
+        <v>190</v>
+      </c>
+      <c r="C19" s="151" t="s">
+        <v>191</v>
+      </c>
+      <c r="D19" s="151" t="s">
+        <v>203</v>
+      </c>
+      <c r="E19" s="151" t="s">
+        <v>192</v>
+      </c>
+      <c r="F19" s="152" t="s">
         <v>193</v>
-      </c>
-      <c r="C19" s="151" t="s">
-        <v>194</v>
-      </c>
-      <c r="D19" s="151" t="s">
-        <v>206</v>
-      </c>
-      <c r="E19" s="151" t="s">
-        <v>195</v>
-      </c>
-      <c r="F19" s="152" t="s">
-        <v>196</v>
       </c>
       <c r="H19" s="143"/>
     </row>
@@ -12790,7 +13017,7 @@
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B50" s="149" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="C50" s="146">
         <f>C$20*(1+Terminal_Growth)^$C$16/Equity_Cost</f>
@@ -12813,7 +13040,7 @@
     <row r="51" spans="1:8" x14ac:dyDescent="0.35">
       <c r="C51" s="137"/>
       <c r="E51" s="150" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="F51" s="160">
         <f>SUM(F20:F50)</f>
@@ -12827,7 +13054,7 @@
     </row>
     <row r="53" spans="1:8" ht="13.15" x14ac:dyDescent="0.35">
       <c r="B53" s="142" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="C53" s="159"/>
       <c r="D53" s="159"/>
@@ -12854,7 +13081,7 @@
       </c>
       <c r="E54" s="154">
         <f>C74</f>
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="F54" s="154">
         <f>C73</f>
@@ -12877,7 +13104,7 @@
         <v>57784.75533129285</v>
       </c>
       <c r="E55" s="146">
-        <v>60774.514925370255</v>
+        <v>66095.2616751311</v>
       </c>
       <c r="F55" s="146">
         <v>66095.2616751311</v>
@@ -12898,7 +13125,7 @@
         <v>59727.305596060905</v>
       </c>
       <c r="E56" s="146">
-        <v>66262.161441924312</v>
+        <v>79564.694983298949</v>
       </c>
       <c r="F56" s="146">
         <v>79564.694983298949</v>
@@ -12919,7 +13146,7 @@
         <v>61925.885670752556</v>
       </c>
       <c r="E57" s="146">
-        <v>72979.737008005875</v>
+        <v>98517.764227230684</v>
       </c>
       <c r="F57" s="146">
         <v>98517.764227230684</v>
@@ -12940,7 +13167,7 @@
         <v>63971.374376136708</v>
       </c>
       <c r="E58" s="146">
-        <v>79774.041778594037</v>
+        <v>120875.73995157168</v>
       </c>
       <c r="F58" s="146">
         <v>120875.73995157168</v>
@@ -12961,7 +13188,7 @@
         <v>65707.869558004182</v>
       </c>
       <c r="E59" s="146">
-        <v>86071.593882588291</v>
+        <v>145347.89471262106</v>
       </c>
       <c r="F59" s="146">
         <v>145347.89471262106</v>
@@ -12982,7 +13209,7 @@
         <v>67105.840940417474</v>
       </c>
       <c r="E60" s="146">
-        <v>91629.284351281254</v>
+        <v>171132.78831832737</v>
       </c>
       <c r="F60" s="146">
         <v>171132.78831832737</v>
@@ -12998,7 +13225,7 @@
     </row>
     <row r="62" spans="1:8" ht="13.15" x14ac:dyDescent="0.35">
       <c r="B62" s="142" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="C62" s="137"/>
       <c r="D62" s="137"/>
@@ -13021,7 +13248,7 @@
       </c>
       <c r="E63" s="155">
         <f>E54</f>
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="F63" s="155">
         <f>F54</f>
@@ -13035,23 +13262,23 @@
       </c>
       <c r="B64" s="147">
         <f>C11</f>
-        <v>2.633837279866718</v>
+        <v>2.9797985390781143</v>
       </c>
       <c r="C64" s="147">
         <f>C11</f>
-        <v>2.633837279866718</v>
+        <v>2.9797985390781143</v>
       </c>
       <c r="D64" s="147">
         <f>C11</f>
-        <v>2.633837279866718</v>
+        <v>2.9797985390781143</v>
       </c>
       <c r="E64" s="164">
         <f>C11</f>
-        <v>2.633837279866718</v>
+        <v>2.9797985390781143</v>
       </c>
       <c r="F64" s="147">
         <f>C11</f>
-        <v>2.633837279866718</v>
+        <v>2.9797985390781143</v>
       </c>
       <c r="H64" s="143"/>
     </row>
@@ -13062,23 +13289,23 @@
       </c>
       <c r="B65" s="147">
         <f t="shared" ref="B65:F70" si="4">(B55-$C$7+$C$8)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>2.1802800522414798</v>
+        <v>2.5262413114528761</v>
       </c>
       <c r="C65" s="147">
         <f t="shared" si="4"/>
-        <v>2.6338372798667167</v>
+        <v>2.9797985390781125</v>
       </c>
       <c r="D65" s="147">
         <f t="shared" si="4"/>
-        <v>2.825522527915719</v>
+        <v>3.1714837871271149</v>
       </c>
       <c r="E65" s="147">
         <f t="shared" si="4"/>
-        <v>3.1248655776922614</v>
+        <v>4.0035548068438391</v>
       </c>
       <c r="F65" s="147">
         <f t="shared" si="4"/>
-        <v>3.6575935476324433</v>
+        <v>4.0035548068438391</v>
       </c>
       <c r="H65" s="143"/>
     </row>
@@ -13089,23 +13316,23 @@
       </c>
       <c r="B66" s="147">
         <f t="shared" si="4"/>
-        <v>1.813781641784463</v>
+        <v>2.1597429009958593</v>
       </c>
       <c r="C66" s="147">
         <f t="shared" si="4"/>
-        <v>2.6338372798667158</v>
+        <v>2.9797985390781117</v>
       </c>
       <c r="D66" s="147">
         <f t="shared" si="4"/>
-        <v>3.0200160657077895</v>
+        <v>3.3659773249191867</v>
       </c>
       <c r="E66" s="147">
         <f t="shared" si="4"/>
-        <v>3.6743040166941845</v>
+        <v>5.3521519493083716</v>
       </c>
       <c r="F66" s="147">
         <f t="shared" si="4"/>
-        <v>5.0061906900969753</v>
+        <v>5.3521519493083716</v>
       </c>
       <c r="H66" s="143"/>
     </row>
@@ -13116,23 +13343,23 @@
       </c>
       <c r="B67" s="147">
         <f t="shared" si="4"/>
-        <v>1.4619960578102331</v>
+        <v>1.807957317021629</v>
       </c>
       <c r="C67" s="147">
         <f t="shared" si="4"/>
-        <v>2.6338372798667158</v>
+        <v>2.9797985390781117</v>
       </c>
       <c r="D67" s="147">
         <f t="shared" si="4"/>
-        <v>3.2401440204904639</v>
+        <v>3.5861052797018607</v>
       </c>
       <c r="E67" s="147">
         <f t="shared" si="4"/>
-        <v>4.3468863744993644</v>
+        <v>7.2497859802663891</v>
       </c>
       <c r="F67" s="147">
         <f t="shared" si="4"/>
-        <v>6.9038247210549928</v>
+        <v>7.2497859802663891</v>
       </c>
       <c r="H67" s="143"/>
     </row>
@@ -13143,23 +13370,23 @@
       </c>
       <c r="B68" s="147">
         <f t="shared" si="4"/>
-        <v>1.1838830342611342</v>
+        <v>1.5298442934725303</v>
       </c>
       <c r="C68" s="147">
         <f t="shared" si="4"/>
-        <v>2.6338372798667145</v>
+        <v>2.9797985390781108</v>
       </c>
       <c r="D68" s="147">
         <f t="shared" si="4"/>
-        <v>3.4449440413905097</v>
+        <v>3.790905300601906</v>
       </c>
       <c r="E68" s="147">
         <f t="shared" si="4"/>
-        <v>5.0271510737641831</v>
+        <v>9.4883287224360657</v>
       </c>
       <c r="F68" s="147">
         <f t="shared" si="4"/>
-        <v>9.1423674632246712</v>
+        <v>9.4883287224360657</v>
       </c>
       <c r="H68" s="143"/>
     </row>
@@ -13170,23 +13397,23 @@
       </c>
       <c r="B69" s="147">
         <f t="shared" si="4"/>
-        <v>0.9825221585393612</v>
+        <v>1.3284834177507572</v>
       </c>
       <c r="C69" s="147">
         <f t="shared" si="4"/>
-        <v>2.6338372798667131</v>
+        <v>2.9797985390781094</v>
       </c>
       <c r="D69" s="147">
         <f t="shared" si="4"/>
-        <v>3.6188067709197331</v>
+        <v>3.964768030131129</v>
       </c>
       <c r="E69" s="147">
         <f t="shared" si="4"/>
-        <v>5.6576795138001934</v>
+        <v>11.938548952613676</v>
       </c>
       <c r="F69" s="147">
         <f t="shared" si="4"/>
-        <v>11.59258769340228</v>
+        <v>11.938548952613676</v>
       </c>
     </row>
     <row r="70" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -13196,40 +13423,40 @@
       </c>
       <c r="B70" s="147">
         <f t="shared" si="4"/>
-        <v>0.84371599729600488</v>
+        <v>1.1896772565074007</v>
       </c>
       <c r="C70" s="147">
         <f t="shared" si="4"/>
-        <v>2.6338372798667131</v>
+        <v>2.9797985390781094</v>
       </c>
       <c r="D70" s="147">
         <f t="shared" si="4"/>
-        <v>3.7587755556811908</v>
+        <v>4.104736814892588</v>
       </c>
       <c r="E70" s="147">
         <f t="shared" si="4"/>
-        <v>6.2141309481925129</v>
+        <v>14.520204248707012</v>
       </c>
       <c r="F70" s="147">
         <f t="shared" si="4"/>
-        <v>14.174242989495616</v>
+        <v>14.520204248707012</v>
       </c>
     </row>
     <row r="72" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B72" s="205" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="C72" s="205" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="D72" s="205" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="E72" s="206" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="F72" s="206" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.35">
@@ -13247,11 +13474,11 @@
       </c>
       <c r="E73" s="158">
         <f>INDEX(B$64:F$70, MATCH(D73, A$64:A$70, 0), MATCH(C73, B$63:F$63, 0))</f>
-        <v>5.0061906900969753</v>
+        <v>5.3521519493083716</v>
       </c>
       <c r="F73" s="207">
         <f>E73*Common_Shares/1000000</f>
-        <v>50000.514983298955</v>
+        <v>53455.884983298958</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.35">
@@ -13261,7 +13488,7 @@
       </c>
       <c r="C74" s="165">
         <f>Scenarios!C51</f>
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="D74" s="168">
         <f>Scenarios!C50</f>
@@ -13269,14 +13496,14 @@
       </c>
       <c r="E74" s="158">
         <f>INDEX(B$64:F$70, MATCH(D74, A$64:A$70, 0), MATCH(C74, B$63:F$63, 0))</f>
-        <v>3.1248655776922614</v>
+        <v>4.0035548068438391</v>
       </c>
       <c r="F74" s="207">
         <f>E74*Common_Shares/1000000</f>
-        <v>31210.334925370258</v>
+        <v>39986.451675131102</v>
       </c>
       <c r="H74" s="143" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.35">
@@ -13294,14 +13521,14 @@
       </c>
       <c r="E75" s="158">
         <f>INDEX(B$64:F$70, MATCH(D75, A$64:A$70, 0), MATCH(C75, B$63:F$63, 0))</f>
-        <v>2.825522527915719</v>
+        <v>3.1714837871271149</v>
       </c>
       <c r="F75" s="207">
         <f>E75*Common_Shares/1000000</f>
-        <v>28220.575331292854</v>
+        <v>31675.945331292849</v>
       </c>
       <c r="H75" s="143" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.35">
@@ -13319,14 +13546,14 @@
       </c>
       <c r="E76" s="158">
         <f>INDEX(B$64:F$70, MATCH(D76, A$64:A$70, 0), MATCH(C76, B$63:F$63, 0))</f>
-        <v>2.6338372798667167</v>
+        <v>2.9797985390781125</v>
       </c>
       <c r="F76" s="207">
         <f>E76*Common_Shares/1000000</f>
-        <v>26306.073525336706</v>
+        <v>29761.443525336705</v>
       </c>
       <c r="H76" s="143" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.35">
@@ -13344,11 +13571,11 @@
       </c>
       <c r="E77" s="158">
         <f>INDEX(B$64:F$70, MATCH(D77, A$64:A$70, 0), MATCH(C77, B$63:F$63, 0))</f>
-        <v>1.813781641784463</v>
+        <v>2.1597429009958593</v>
       </c>
       <c r="F77" s="207">
         <f>E77*Common_Shares/1000000</f>
-        <v>18115.573650815099</v>
+        <v>21570.943650815101</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.35">
@@ -13403,7 +13630,7 @@
   <sheetData>
     <row r="2" spans="2:7" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B2" s="37" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C2" s="38"/>
       <c r="D2" s="38"/>
@@ -13413,105 +13640,105 @@
     </row>
     <row r="3" spans="2:7" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B3" s="186" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B4" s="176" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="C4" s="143">
         <v>4</v>
       </c>
       <c r="D4" s="143"/>
       <c r="E4" s="119" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
     </row>
     <row r="6" spans="2:7" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B6" s="186" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C6" s="127">
         <f>Valuation_Model!C3</f>
         <v>1000000</v>
       </c>
       <c r="E6" s="119" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B7" s="119" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="C7" s="137">
         <f>Normalized_FCF!G19</f>
         <v>-107.89999999999637</v>
       </c>
-      <c r="E7" s="264" t="s">
-        <v>267</v>
+      <c r="E7" s="265" t="s">
+        <v>263</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B8" s="119" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C8" s="137">
         <f>Normalized_FCF!C19</f>
         <v>5587.025352533672</v>
       </c>
-      <c r="E8" s="265"/>
+      <c r="E8" s="266"/>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="E9" s="265"/>
+      <c r="E9" s="266"/>
     </row>
     <row r="10" spans="2:7" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B10" s="186" t="s">
-        <v>251</v>
-      </c>
-      <c r="E10" s="265"/>
+        <v>247</v>
+      </c>
+      <c r="E10" s="266"/>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B11" s="141" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="C11" s="185">
-        <f>AVERAGE(Normalized_FCF!G98:INDEX(Normalized_FCF!G98:Q98, $C$4))</f>
+        <f>AVERAGE(Normalized_FCF!G94:INDEX(Normalized_FCF!G94:Q94, $C$4))</f>
         <v>0.18790429589393956</v>
       </c>
       <c r="D11" s="185"/>
-      <c r="E11" s="265"/>
+      <c r="E11" s="266"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B12" s="171" t="s">
-        <v>248</v>
-      </c>
-      <c r="E12" s="265"/>
+        <v>244</v>
+      </c>
+      <c r="E12" s="266"/>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B13" s="119" t="s">
-        <v>144</v>
-      </c>
-      <c r="E13" s="265"/>
+        <v>143</v>
+      </c>
+      <c r="E13" s="266"/>
     </row>
     <row r="15" spans="2:7" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B15" s="186" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B16" s="119" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B17" s="171" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="19" spans="2:7" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B19" s="37" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="C19" s="38"/>
       <c r="D19" s="38"/>
@@ -13521,37 +13748,37 @@
     </row>
     <row r="20" spans="2:7" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B20" s="131" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="E20" s="186" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B21" s="119" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="C21" s="187">
         <f>Valuation_Model!E76</f>
-        <v>2.6338372798667167</v>
+        <v>2.9797985390781125</v>
       </c>
       <c r="D21" t="str">
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
       <c r="E21" s="198" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
     </row>
     <row r="23" spans="2:7" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B23" s="131" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="E23" s="199"/>
     </row>
     <row r="24" spans="2:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B24" s="176" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="C24" s="174">
         <v>15</v>
@@ -13561,7 +13788,7 @@
     </row>
     <row r="25" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B25" s="141" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="C25" s="175">
         <v>0.12</v>
@@ -13571,24 +13798,24 @@
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B26" s="119" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="C26" s="187">
         <f>Valuation_Model!C17</f>
-        <v>8.2533716119364087</v>
+        <v>8.599332871147805</v>
       </c>
       <c r="D26" s="187"/>
       <c r="E26" s="200"/>
     </row>
     <row r="28" spans="2:7" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B28" s="131" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="C28" s="178"/>
     </row>
     <row r="29" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B29" s="119" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="C29">
         <f>Market_Price</f>
@@ -13597,7 +13824,7 @@
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B30" s="119" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="C30">
         <v>13</v>
@@ -13605,12 +13832,12 @@
     </row>
     <row r="31" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B31" s="119" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="33" spans="2:7" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B33" s="37" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="C33" s="38"/>
       <c r="D33" s="38"/>
@@ -13620,12 +13847,12 @@
     </row>
     <row r="34" spans="2:7" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B34" s="131" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B35" s="176" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="C35" s="174">
         <v>5</v>
@@ -13634,171 +13861,171 @@
     </row>
     <row r="37" spans="2:7" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B37" s="186" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="E37" s="186" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
     </row>
     <row r="38" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B38" s="176" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="C38" s="193">
         <f>C35</f>
         <v>5</v>
       </c>
       <c r="D38" s="190"/>
-      <c r="E38" s="265"/>
+      <c r="E38" s="266"/>
     </row>
     <row r="39" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B39" s="141" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="C39" s="191">
         <v>0.02</v>
       </c>
       <c r="D39" s="191"/>
-      <c r="E39" s="265"/>
+      <c r="E39" s="266"/>
     </row>
     <row r="40" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B40" s="119" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="C40" s="187">
         <f>Valuation_Model!E75</f>
-        <v>2.825522527915719</v>
+        <v>3.1714837871271149</v>
       </c>
       <c r="D40" s="187" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E40" s="265"/>
+      <c r="E40" s="266"/>
     </row>
     <row r="41" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B41" s="119" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="C41" s="192">
         <v>0.6</v>
       </c>
       <c r="D41" s="192"/>
-      <c r="E41" s="265"/>
+      <c r="E41" s="266"/>
     </row>
     <row r="43" spans="2:7" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B43" s="186" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="E43" s="186" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
     </row>
     <row r="44" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B44" s="176" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="C44" s="193">
         <f>C35</f>
         <v>5</v>
       </c>
       <c r="D44" s="190"/>
-      <c r="E44" s="265"/>
+      <c r="E44" s="266"/>
     </row>
     <row r="45" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B45" s="141" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="C45" s="191">
         <v>0</v>
       </c>
       <c r="D45" s="191"/>
-      <c r="E45" s="265"/>
+      <c r="E45" s="266"/>
     </row>
     <row r="46" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B46" s="119" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="C46" s="187">
         <f>Valuation_Model!E76</f>
-        <v>2.6338372798667167</v>
+        <v>2.9797985390781125</v>
       </c>
       <c r="D46" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E46" s="265"/>
+      <c r="E46" s="266"/>
     </row>
     <row r="47" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B47" s="119" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="C47" s="192">
         <v>0.2</v>
       </c>
       <c r="D47" s="192"/>
-      <c r="E47" s="265"/>
+      <c r="E47" s="266"/>
     </row>
     <row r="49" spans="2:7" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B49" s="186" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="E49" s="186" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
     </row>
     <row r="50" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B50" s="176" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="C50" s="193">
         <f>C35</f>
         <v>5</v>
       </c>
       <c r="D50" s="190"/>
-      <c r="E50" s="265"/>
+      <c r="E50" s="266"/>
     </row>
     <row r="51" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B51" s="141" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="C51" s="191">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="D51" s="191"/>
-      <c r="E51" s="265"/>
+      <c r="E51" s="266"/>
     </row>
     <row r="52" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B52" s="119" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="C52" s="187">
         <f>Valuation_Model!E74</f>
-        <v>3.1248655776922614</v>
+        <v>4.0035548068438391</v>
       </c>
       <c r="D52" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E52" s="265"/>
+      <c r="E52" s="266"/>
     </row>
     <row r="53" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B53" s="119" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="C53" s="195">
         <f>1-C41-C47</f>
         <v>0.2</v>
       </c>
       <c r="D53" s="192"/>
-      <c r="E53" s="265"/>
+      <c r="E53" s="266"/>
     </row>
     <row r="55" spans="2:7" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B55" s="119" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="C55" s="180">
         <f>C40*C41+C46*C47+C52*C53</f>
-        <v>2.8470540882612272</v>
+        <v>3.2995609414606593</v>
       </c>
       <c r="D55" t="str">
         <f>Market_currency</f>
@@ -13807,7 +14034,7 @@
     </row>
     <row r="57" spans="2:7" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B57" s="37" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="C57" s="38"/>
       <c r="D57" s="38"/>
@@ -13817,12 +14044,12 @@
     </row>
     <row r="58" spans="2:7" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B58" s="131" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
     </row>
     <row r="59" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B59" s="176" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="C59" s="174">
         <v>10</v>
@@ -13835,119 +14062,119 @@
     </row>
     <row r="61" spans="2:7" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B61" s="186" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="E61" s="186" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
     </row>
     <row r="62" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B62" s="176" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="C62" s="193">
         <f>C59</f>
         <v>10</v>
       </c>
       <c r="D62" s="190"/>
-      <c r="E62" s="264" t="s">
-        <v>266</v>
+      <c r="E62" s="265" t="s">
+        <v>262</v>
       </c>
     </row>
     <row r="63" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B63" s="141" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="C63" s="191">
         <v>-0.05</v>
       </c>
       <c r="D63" s="191"/>
-      <c r="E63" s="265"/>
+      <c r="E63" s="266"/>
     </row>
     <row r="64" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B64" s="119" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="C64" s="187">
         <f>Valuation_Model!E77</f>
-        <v>1.813781641784463</v>
+        <v>2.1597429009958593</v>
       </c>
       <c r="D64" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E64" s="265"/>
+      <c r="E64" s="266"/>
     </row>
     <row r="65" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B65" s="119" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="C65" s="192">
         <v>0.1</v>
       </c>
       <c r="D65" s="192"/>
-      <c r="E65" s="265"/>
+      <c r="E65" s="266"/>
     </row>
     <row r="67" spans="2:7" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B67" s="186" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="E67" s="186" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
     </row>
     <row r="68" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B68" s="176" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="C68" s="193">
         <f>C59</f>
         <v>10</v>
       </c>
       <c r="D68" s="190"/>
-      <c r="E68" s="264"/>
+      <c r="E68" s="265"/>
     </row>
     <row r="69" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B69" s="141" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="C69" s="191">
         <v>0.1</v>
       </c>
       <c r="D69" s="191"/>
-      <c r="E69" s="265"/>
+      <c r="E69" s="266"/>
     </row>
     <row r="70" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B70" s="119" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="C70" s="187">
         <f>Valuation_Model!E73</f>
-        <v>5.0061906900969753</v>
+        <v>5.3521519493083716</v>
       </c>
       <c r="D70" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E70" s="265"/>
+      <c r="E70" s="266"/>
     </row>
     <row r="71" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B71" s="119" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="C71" s="192">
         <v>0.1</v>
       </c>
       <c r="D71" s="192"/>
-      <c r="E71" s="265"/>
+      <c r="E71" s="266"/>
     </row>
     <row r="73" spans="2:7" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B73" s="119" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="C73" s="180">
         <f>C64*C65+C70*C71+C55*(1-C65-C71)</f>
-        <v>2.9596405037971256</v>
+        <v>3.3908382381989508</v>
       </c>
       <c r="D73" t="str">
         <f>Market_currency</f>
@@ -13956,7 +14183,7 @@
     </row>
     <row r="75" spans="2:7" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B75" s="37" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="C75" s="38"/>
       <c r="D75" s="38"/>
@@ -13966,15 +14193,15 @@
     </row>
     <row r="76" spans="2:7" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B76" s="131" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="E76" s="131" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
     </row>
     <row r="77" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B77" s="119" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="C77" s="195">
         <f>Thesis!C68</f>
@@ -13982,7 +14209,7 @@
       </c>
       <c r="D77" s="157"/>
       <c r="E77" s="119" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="F77" s="193">
         <f>Thesis!C67</f>
@@ -13991,10 +14218,10 @@
     </row>
     <row r="78" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B78" s="119" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="C78" s="209">
-        <f>Normalized_FCF!C93</f>
+        <f>Normalized_FCF!C89</f>
         <v>0.55000000000000004</v>
       </c>
       <c r="D78" t="str">
@@ -14002,17 +14229,17 @@
         <v>HKD</v>
       </c>
       <c r="E78" s="119" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
     </row>
     <row r="80" spans="2:7" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B80" s="131" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
     </row>
     <row r="81" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B81" s="119" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="C81" s="139">
         <f>PV(C77, F77, -C78, 0)</f>
@@ -14023,35 +14250,35 @@
     </row>
     <row r="82" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B82" s="119" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="C82" s="139">
         <f>C73/(1+C77)^F77</f>
-        <v>1.7127549211788922</v>
+        <v>1.9622906471058743</v>
       </c>
       <c r="D82" s="139"/>
     </row>
     <row r="83" spans="2:9" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B83" s="133" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="C83" s="134">
         <f>C81+C82</f>
-        <v>2.8713197359937066</v>
+        <v>3.120855461920689</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
       <c r="E83" s="196" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="F83" s="197">
         <f>(C83/C73-1)</f>
-        <v>-2.984172155033904E-2</v>
+        <v>-7.9621249175738762E-2</v>
       </c>
       <c r="I83" s="143" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
     </row>
     <row r="86" spans="2:9" x14ac:dyDescent="0.35">
